--- a/data/source/weekly/cs-en-us-107pct.xlsx
+++ b/data/source/weekly/cs-en-us-107pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">7</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/2/2026</t>
+      <t xml:space="preserve">2/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/8/2026</t>
+      <t xml:space="preserve">2/15/2026</t>
     </r>
   </si>
   <si>
@@ -202,10 +202,10 @@
     <t>0</t>
   </si>
   <si>
+    <t>Rape</t>
+  </si>
+  <si>
     <t>***.*</t>
-  </si>
-  <si>
-    <t>Rape</t>
   </si>
   <si>
     <t>Robbery</t>
@@ -854,11 +854,11 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>21</v>
+      <c r="D14" s="14">
+        <v>1</v>
+      </c>
+      <c r="E14" s="15">
+        <v>-100</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
@@ -873,7 +873,7 @@
         <v>20</v>
       </c>
       <c r="J14" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K14" s="15">
         <v>-100</v>
@@ -884,13 +884,13 @@
       <c r="M14" s="15">
         <v>-100</v>
       </c>
-      <c r="N14" s="13" t="s">
-        <v>21</v>
+      <c r="N14" s="15">
+        <v>-100</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C15" s="13" t="s">
         <v>20</v>
@@ -899,16 +899,16 @@
         <v>20</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F15" s="14">
-        <v>2</v>
-      </c>
-      <c r="G15" s="14">
-        <v>1</v>
-      </c>
-      <c r="H15" s="15">
-        <v>100</v>
+        <v>22</v>
+      </c>
+      <c r="F15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="I15" s="14">
         <v>2</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D16" s="14">
         <v>4</v>
       </c>
       <c r="E16" s="15">
-        <v>-25</v>
+        <v>25</v>
       </c>
       <c r="F16" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G16" s="14">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H16" s="15">
-        <v>28.571428571428</v>
+        <v>0</v>
       </c>
       <c r="I16" s="14">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J16" s="14">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="K16" s="15">
-        <v>-16.666666666666</v>
+        <v>-6.25</v>
       </c>
       <c r="L16" s="15">
         <v>0</v>
       </c>
       <c r="M16" s="15">
-        <v>-78.260869565217</v>
+        <v>-68.085106382978</v>
       </c>
       <c r="N16" s="15">
-        <v>-91.452991452991</v>
+        <v>-88.970588235294</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D17" s="14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E17" s="15">
-        <v>200</v>
+        <v>-60</v>
       </c>
       <c r="F17" s="14">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G17" s="14">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H17" s="15">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="I17" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J17" s="14">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="K17" s="15">
-        <v>-34.782608695652</v>
+        <v>-39.285714285714</v>
       </c>
       <c r="L17" s="15">
-        <v>-51.612903225806</v>
+        <v>-50</v>
       </c>
       <c r="M17" s="15">
-        <v>25</v>
+        <v>30.769230769230</v>
       </c>
       <c r="N17" s="15">
-        <v>-55.882352941176</v>
+        <v>-56.410256410256</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1025,31 +1025,31 @@
         <v>-20</v>
       </c>
       <c r="F18" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G18" s="14">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H18" s="15">
-        <v>-31.818181818181</v>
+        <v>-20</v>
       </c>
       <c r="I18" s="14">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J18" s="14">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="K18" s="15">
-        <v>-50</v>
+        <v>-46.153846153846</v>
       </c>
       <c r="L18" s="15">
-        <v>-37.037037037037</v>
+        <v>-38.235294117647</v>
       </c>
       <c r="M18" s="15">
-        <v>-48.484848484848</v>
+        <v>-44.736842105263</v>
       </c>
       <c r="N18" s="15">
-        <v>-92.543859649122</v>
+        <v>-91.633466135458</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
+        <v>9</v>
+      </c>
+      <c r="D19" s="14">
         <v>10</v>
       </c>
-      <c r="D19" s="14">
-        <v>9</v>
-      </c>
       <c r="E19" s="15">
-        <v>11.111111111111</v>
+        <v>-10</v>
       </c>
       <c r="F19" s="14">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G19" s="14">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H19" s="15">
-        <v>-20.930232558139</v>
+        <v>-14.634146341463</v>
       </c>
       <c r="I19" s="14">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="J19" s="14">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="K19" s="15">
-        <v>12.5</v>
+        <v>10.344827586206</v>
       </c>
       <c r="L19" s="15">
-        <v>-16.923076923076</v>
+        <v>-17.948717948717</v>
       </c>
       <c r="M19" s="15">
-        <v>-5.263157894736</v>
+        <v>0</v>
       </c>
       <c r="N19" s="15">
-        <v>1.886792452830</v>
+        <v>3.225806451612</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D20" s="14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E20" s="15">
-        <v>-70</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="F20" s="14">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G20" s="14">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="H20" s="15">
-        <v>-33.333333333333</v>
+        <v>-53.333333333333</v>
       </c>
       <c r="I20" s="14">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="J20" s="14">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="K20" s="15">
-        <v>-33.333333333333</v>
+        <v>-32.653061224489</v>
       </c>
       <c r="L20" s="15">
-        <v>-17.647058823529</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="M20" s="15">
-        <v>7.692307692307</v>
+        <v>22.222222222222</v>
       </c>
       <c r="N20" s="15">
-        <v>-94.656488549618</v>
+        <v>-94.581280788177</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D21" s="17">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E21" s="18">
-        <v>-20.689655172413</v>
+        <v>-21.875</v>
       </c>
       <c r="F21" s="17">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="G21" s="17">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="H21" s="18">
-        <v>-25</v>
+        <v>-30.645161290322</v>
       </c>
       <c r="I21" s="17">
-        <v>126</v>
+        <v>152</v>
       </c>
       <c r="J21" s="17">
-        <v>162</v>
+        <v>194</v>
       </c>
       <c r="K21" s="18">
-        <v>-22.222222222222</v>
+        <v>-21.649484536082</v>
       </c>
       <c r="L21" s="18">
-        <v>-25.882352941176</v>
+        <v>-24</v>
       </c>
       <c r="M21" s="18">
-        <v>-28.409090909090</v>
+        <v>-20.418848167539</v>
       </c>
       <c r="N21" s="18">
-        <v>-86.875</v>
+        <v>-86.206896551724</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,54 +1180,54 @@
         <v>29</v>
       </c>
       <c r="C22" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F22" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G22" s="14">
         <v>2</v>
       </c>
       <c r="H22" s="15">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="I22" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J22" s="14">
         <v>2</v>
       </c>
       <c r="K22" s="15">
-        <v>200</v>
+        <v>350</v>
       </c>
       <c r="L22" s="15">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="M22" s="15">
-        <v>200</v>
+        <v>350</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
+      <c r="C23" s="14">
+        <v>1</v>
       </c>
       <c r="D23" s="14">
         <v>1</v>
       </c>
       <c r="E23" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F23" s="14">
         <v>2</v>
@@ -1239,22 +1239,22 @@
         <v>0</v>
       </c>
       <c r="I23" s="14">
+        <v>5</v>
+      </c>
+      <c r="J23" s="14">
         <v>4</v>
       </c>
-      <c r="J23" s="14">
-        <v>3</v>
-      </c>
       <c r="K23" s="15">
-        <v>33.333333333333</v>
+        <v>25</v>
       </c>
       <c r="L23" s="15">
-        <v>-42.857142857142</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="M23" s="15">
-        <v>-33.333333333333</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D24" s="14">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="E24" s="15">
-        <v>-56.25</v>
+        <v>31.25</v>
       </c>
       <c r="F24" s="14">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="G24" s="14">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H24" s="15">
-        <v>-15.384615384615</v>
+        <v>-26.086956521739</v>
       </c>
       <c r="I24" s="14">
-        <v>109</v>
+        <v>130</v>
       </c>
       <c r="J24" s="14">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="K24" s="15">
-        <v>1.869158878504</v>
+        <v>5.691056910569</v>
       </c>
       <c r="L24" s="15">
-        <v>-6.837606837606</v>
+        <v>-10.344827586206</v>
       </c>
       <c r="M24" s="15">
-        <v>26.744186046511</v>
+        <v>41.304347826087</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1303,40 +1303,40 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D25" s="14">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E25" s="15">
-        <v>-88.888888888888</v>
+        <v>20</v>
       </c>
       <c r="F25" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G25" s="14">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H25" s="15">
-        <v>-73.809523809523</v>
+        <v>-70.454545454545</v>
       </c>
       <c r="I25" s="14">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J25" s="14">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="K25" s="15">
-        <v>-63.043478260869</v>
+        <v>-54.901960784313</v>
       </c>
       <c r="L25" s="15">
-        <v>-67.307692307692</v>
+        <v>-65.671641791044</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1344,63 +1344,63 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D26" s="14">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E26" s="15">
-        <v>-50</v>
+        <v>-60</v>
       </c>
       <c r="F26" s="14">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G26" s="14">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="H26" s="15">
-        <v>-41.176470588235</v>
+        <v>-47.916666666666</v>
       </c>
       <c r="I26" s="14">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="J26" s="14">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="K26" s="15">
-        <v>-40.298507462686</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="L26" s="15">
-        <v>-6.976744186046</v>
+        <v>-12</v>
       </c>
       <c r="M26" s="15">
-        <v>-4.761904761904</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="F27" s="14">
         <v>2</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F27" s="14">
-        <v>4</v>
-      </c>
-      <c r="G27" s="14">
-        <v>1</v>
-      </c>
-      <c r="H27" s="15">
-        <v>300</v>
+      <c r="G27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H27" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="I27" s="14">
         <v>4</v>
@@ -1415,51 +1415,51 @@
         <v>0</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="14">
+        <v>2</v>
       </c>
       <c r="D28" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E28" s="15">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="F28" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G28" s="14">
         <v>3</v>
       </c>
       <c r="H28" s="15">
-        <v>33.333333333333</v>
+        <v>100</v>
       </c>
       <c r="I28" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J28" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K28" s="15">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="L28" s="15">
-        <v>0</v>
+        <v>28.571428571428</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29" spans="1:14">
@@ -1469,17 +1469,17 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="D29" s="14">
+        <v>1</v>
+      </c>
+      <c r="E29" s="15">
+        <v>-100</v>
       </c>
       <c r="F29" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H29" s="15">
         <v>-100</v>
@@ -1488,7 +1488,7 @@
         <v>20</v>
       </c>
       <c r="J29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K29" s="15">
         <v>-100</v>
@@ -1510,17 +1510,17 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="D30" s="14">
+        <v>1</v>
+      </c>
+      <c r="E30" s="15">
+        <v>-100</v>
       </c>
       <c r="F30" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H30" s="15">
         <v>-100</v>
@@ -1529,7 +1529,7 @@
         <v>20</v>
       </c>
       <c r="J30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K30" s="15">
         <v>-100</v>
@@ -1555,13 +1555,13 @@
         <v>20</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G31" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H31" s="15">
         <v>-100</v>
@@ -1576,13 +1576,13 @@
         <v>-100</v>
       </c>
       <c r="L31" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1614,7 +1614,7 @@
         <v>20</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>
@@ -1623,7 +1623,7 @@
         <v>20</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I33" s="13" t="s">
         <v>20</v>
@@ -1632,16 +1632,16 @@
         <v>20</v>
       </c>
       <c r="K33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C40" s="14">
         <v>24</v>

--- a/data/source/weekly/cs-en-us-107pct.xlsx
+++ b/data/source/weekly/cs-en-us-107pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t xml:space="preserve">8</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/9/2026</t>
+      <t xml:space="preserve">2/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/15/2026</t>
+      <t xml:space="preserve">2/22/2026</t>
     </r>
   </si>
   <si>
@@ -202,10 +202,10 @@
     <t>0</t>
   </si>
   <si>
+    <t>***.*</t>
+  </si>
+  <si>
     <t>Rape</t>
-  </si>
-  <si>
-    <t>***.*</t>
   </si>
   <si>
     <t>Robbery</t>
@@ -854,11 +854,11 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="14">
-        <v>1</v>
-      </c>
-      <c r="E14" s="15">
-        <v>-100</v>
+      <c r="D14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
@@ -890,84 +890,84 @@
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="F15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>22</v>
+      <c r="C15" s="14">
+        <v>1</v>
+      </c>
+      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>0</v>
+      </c>
+      <c r="F15" s="14">
+        <v>1</v>
+      </c>
+      <c r="G15" s="14">
+        <v>1</v>
+      </c>
+      <c r="H15" s="15">
+        <v>0</v>
       </c>
       <c r="I15" s="14">
+        <v>3</v>
+      </c>
+      <c r="J15" s="14">
         <v>2</v>
       </c>
-      <c r="J15" s="14">
-        <v>1</v>
-      </c>
       <c r="K15" s="15">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="L15" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M15" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N15" s="15">
-        <v>-50</v>
+        <v>-40</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="14">
-        <v>5</v>
+      <c r="C16" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D16" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E16" s="15">
-        <v>25</v>
+        <v>-100</v>
       </c>
       <c r="F16" s="14">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G16" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H16" s="15">
-        <v>0</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="I16" s="14">
         <v>15</v>
       </c>
       <c r="J16" s="14">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K16" s="15">
-        <v>-6.25</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="L16" s="15">
         <v>0</v>
       </c>
       <c r="M16" s="15">
-        <v>-68.085106382978</v>
+        <v>-69.387755102040</v>
       </c>
       <c r="N16" s="15">
-        <v>-88.970588235294</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D17" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E17" s="15">
-        <v>-60</v>
+        <v>25</v>
       </c>
       <c r="F17" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G17" s="14">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H17" s="15">
-        <v>-50</v>
+        <v>-23.529411764705</v>
       </c>
       <c r="I17" s="14">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J17" s="14">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="K17" s="15">
-        <v>-39.285714285714</v>
+        <v>-31.25</v>
       </c>
       <c r="L17" s="15">
-        <v>-50</v>
+        <v>-42.105263157894</v>
       </c>
       <c r="M17" s="15">
-        <v>30.769230769230</v>
+        <v>57.142857142857</v>
       </c>
       <c r="N17" s="15">
-        <v>-56.410256410256</v>
+        <v>-45</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
-        <v>4</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D18" s="14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E18" s="15">
-        <v>-20</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="14">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="G18" s="14">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H18" s="15">
-        <v>-20</v>
+        <v>-47.058823529411</v>
       </c>
       <c r="I18" s="14">
         <v>21</v>
       </c>
       <c r="J18" s="14">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K18" s="15">
-        <v>-46.153846153846</v>
+        <v>-47.5</v>
       </c>
       <c r="L18" s="15">
-        <v>-38.235294117647</v>
+        <v>-44.736842105263</v>
       </c>
       <c r="M18" s="15">
-        <v>-44.736842105263</v>
+        <v>-47.5</v>
       </c>
       <c r="N18" s="15">
-        <v>-91.633466135458</v>
+        <v>-92.579505300353</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
+        <v>6</v>
+      </c>
+      <c r="D19" s="14">
         <v>9</v>
       </c>
-      <c r="D19" s="14">
-        <v>10</v>
-      </c>
       <c r="E19" s="15">
-        <v>-10</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F19" s="14">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G19" s="14">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H19" s="15">
-        <v>-14.634146341463</v>
+        <v>-23.809523809523</v>
       </c>
       <c r="I19" s="14">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="J19" s="14">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="K19" s="15">
-        <v>10.344827586206</v>
+        <v>2.985074626865</v>
       </c>
       <c r="L19" s="15">
-        <v>-17.948717948717</v>
+        <v>-21.590909090909</v>
       </c>
       <c r="M19" s="15">
-        <v>0</v>
+        <v>-6.756756756756</v>
       </c>
       <c r="N19" s="15">
-        <v>3.225806451612</v>
+        <v>-2.816901408450</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
+        <v>4</v>
+      </c>
+      <c r="D20" s="14">
         <v>5</v>
       </c>
-      <c r="D20" s="14">
-        <v>7</v>
-      </c>
       <c r="E20" s="15">
-        <v>-28.571428571428</v>
+        <v>-20</v>
       </c>
       <c r="F20" s="14">
         <v>14</v>
       </c>
       <c r="G20" s="14">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H20" s="15">
-        <v>-53.333333333333</v>
+        <v>-54.838709677419</v>
       </c>
       <c r="I20" s="14">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J20" s="14">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="K20" s="15">
-        <v>-32.653061224489</v>
+        <v>-31.481481481481</v>
       </c>
       <c r="L20" s="15">
-        <v>-8.333333333333</v>
+        <v>-9.756097560975</v>
       </c>
       <c r="M20" s="15">
-        <v>22.222222222222</v>
+        <v>27.586206896551</v>
       </c>
       <c r="N20" s="15">
-        <v>-94.581280788177</v>
+        <v>-94.706723891273</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,63 +1139,63 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D21" s="17">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E21" s="18">
-        <v>-21.875</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="F21" s="17">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="G21" s="17">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H21" s="18">
-        <v>-30.645161290322</v>
+        <v>-36.585365853658</v>
       </c>
       <c r="I21" s="17">
-        <v>152</v>
+        <v>167</v>
       </c>
       <c r="J21" s="17">
-        <v>194</v>
+        <v>216</v>
       </c>
       <c r="K21" s="18">
-        <v>-21.649484536082</v>
+        <v>-22.685185185185</v>
       </c>
       <c r="L21" s="18">
-        <v>-24</v>
+        <v>-25.112107623318</v>
       </c>
       <c r="M21" s="18">
-        <v>-20.418848167539</v>
+        <v>-19.711538461538</v>
       </c>
       <c r="N21" s="18">
-        <v>-86.206896551724</v>
+        <v>-86.629303442754</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>3</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F22" s="14">
         <v>6</v>
       </c>
       <c r="G22" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H22" s="15">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="I22" s="14">
         <v>9</v>
@@ -1210,42 +1210,42 @@
         <v>50</v>
       </c>
       <c r="M22" s="15">
-        <v>350</v>
+        <v>200</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="14">
-        <v>1</v>
+      <c r="C23" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D23" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E23" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F23" s="14">
         <v>2</v>
       </c>
       <c r="G23" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H23" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I23" s="14">
         <v>5</v>
       </c>
       <c r="J23" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K23" s="15">
-        <v>25</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="L23" s="15">
         <v>-28.571428571428</v>
@@ -1254,7 +1254,7 @@
         <v>-16.666666666666</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D24" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E24" s="15">
-        <v>31.25</v>
+        <v>29.411764705882</v>
       </c>
       <c r="F24" s="14">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="G24" s="14">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="H24" s="15">
-        <v>-26.086956521739</v>
+        <v>-22.105263157894</v>
       </c>
       <c r="I24" s="14">
-        <v>130</v>
+        <v>152</v>
       </c>
       <c r="J24" s="14">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="K24" s="15">
-        <v>5.691056910569</v>
+        <v>8.571428571428</v>
       </c>
       <c r="L24" s="15">
-        <v>-10.344827586206</v>
+        <v>-7.878787878787</v>
       </c>
       <c r="M24" s="15">
-        <v>41.304347826087</v>
+        <v>46.153846153846</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1303,40 +1303,40 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D25" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E25" s="15">
-        <v>20</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F25" s="14">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G25" s="14">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H25" s="15">
-        <v>-70.454545454545</v>
+        <v>-79.069767441860</v>
       </c>
       <c r="I25" s="14">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J25" s="14">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="K25" s="15">
-        <v>-54.901960784313</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="L25" s="15">
-        <v>-65.671641791044</v>
+        <v>-67.567567567567</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1344,81 +1344,81 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D26" s="14">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E26" s="15">
-        <v>-60</v>
+        <v>-26.666666666666</v>
       </c>
       <c r="F26" s="14">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="G26" s="14">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="H26" s="15">
-        <v>-47.916666666666</v>
+        <v>-42.307692307692</v>
       </c>
       <c r="I26" s="14">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="J26" s="14">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="K26" s="15">
-        <v>-42.857142857142</v>
+        <v>-40.217391304347</v>
       </c>
       <c r="L26" s="15">
-        <v>-12</v>
+        <v>-5.172413793103</v>
       </c>
       <c r="M26" s="15">
-        <v>-15.384615384615</v>
+        <v>1.851851851851</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>22</v>
+      <c r="C27" s="14">
+        <v>1</v>
+      </c>
+      <c r="D27" s="14">
+        <v>2</v>
+      </c>
+      <c r="E27" s="15">
+        <v>-50</v>
       </c>
       <c r="F27" s="14">
+        <v>3</v>
+      </c>
+      <c r="G27" s="14">
         <v>2</v>
       </c>
-      <c r="G27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H27" s="13" t="s">
-        <v>22</v>
+      <c r="H27" s="15">
+        <v>50</v>
       </c>
       <c r="I27" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J27" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K27" s="15">
-        <v>300</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L27" s="15">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -1435,31 +1435,31 @@
         <v>100</v>
       </c>
       <c r="F28" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G28" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H28" s="15">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="I28" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J28" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K28" s="15">
-        <v>50</v>
+        <v>57.142857142857</v>
       </c>
       <c r="L28" s="15">
-        <v>28.571428571428</v>
+        <v>57.142857142857</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:14">
@@ -1469,11 +1469,11 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="14">
-        <v>1</v>
-      </c>
-      <c r="E29" s="15">
-        <v>-100</v>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F29" s="13" t="s">
         <v>20</v>
@@ -1510,11 +1510,11 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="14">
-        <v>1</v>
-      </c>
-      <c r="E30" s="15">
-        <v>-100</v>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F30" s="13" t="s">
         <v>20</v>
@@ -1548,41 +1548,41 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
+      <c r="C31" s="14">
+        <v>1</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F31" s="13" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="F31" s="14">
+        <v>2</v>
       </c>
       <c r="G31" s="14">
+        <v>1</v>
+      </c>
+      <c r="H31" s="15">
+        <v>100</v>
+      </c>
+      <c r="I31" s="14">
         <v>2</v>
-      </c>
-      <c r="H31" s="15">
-        <v>-100</v>
-      </c>
-      <c r="I31" s="13" t="s">
-        <v>20</v>
       </c>
       <c r="J31" s="14">
         <v>3</v>
       </c>
       <c r="K31" s="15">
-        <v>-100</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1614,7 +1614,7 @@
         <v>20</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>
@@ -1623,7 +1623,7 @@
         <v>20</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I33" s="13" t="s">
         <v>20</v>
@@ -1632,16 +1632,16 @@
         <v>20</v>
       </c>
       <c r="K33" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="L33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
+      </c>
+      <c r="L33" s="15">
+        <v>-100</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C40" s="14">
         <v>24</v>

--- a/data/source/weekly/cs-en-us-107pct.xlsx
+++ b/data/source/weekly/cs-en-us-107pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">8</t>
+      <t xml:space="preserve">9</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/16/2026</t>
+      <t xml:space="preserve">2/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/22/2026</t>
+      <t xml:space="preserve">3/1/2026</t>
     </r>
   </si>
   <si>
@@ -864,7 +864,7 @@
         <v>20</v>
       </c>
       <c r="G14" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H14" s="15">
         <v>-100</v>
@@ -895,79 +895,79 @@
       <c r="C15" s="14">
         <v>1</v>
       </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>0</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" s="14">
         <v>1</v>
       </c>
       <c r="H15" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I15" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J15" s="14">
         <v>2</v>
       </c>
       <c r="K15" s="15">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L15" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M15" s="15">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="N15" s="15">
-        <v>-40</v>
+        <v>-33.333333333333</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
+      <c r="C16" s="14">
+        <v>3</v>
       </c>
       <c r="D16" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16" s="15">
-        <v>-100</v>
+        <v>200</v>
       </c>
       <c r="F16" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G16" s="14">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H16" s="15">
-        <v>-30.769230769230</v>
+        <v>0</v>
       </c>
       <c r="I16" s="14">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J16" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K16" s="15">
-        <v>-16.666666666666</v>
+        <v>-5.263157894736</v>
       </c>
       <c r="L16" s="15">
         <v>0</v>
       </c>
       <c r="M16" s="15">
-        <v>-69.387755102040</v>
+        <v>-64.705882352941</v>
       </c>
       <c r="N16" s="15">
-        <v>-90</v>
+        <v>-89.090909090909</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D17" s="14">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E17" s="15">
-        <v>25</v>
+        <v>-50</v>
       </c>
       <c r="F17" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G17" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H17" s="15">
-        <v>-23.529411764705</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="I17" s="14">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J17" s="14">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="K17" s="15">
-        <v>-31.25</v>
+        <v>-35</v>
       </c>
       <c r="L17" s="15">
-        <v>-42.105263157894</v>
+        <v>-48</v>
       </c>
       <c r="M17" s="15">
-        <v>57.142857142857</v>
+        <v>62.5</v>
       </c>
       <c r="N17" s="15">
-        <v>-45</v>
+        <v>-40.909090909090</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="14">
+        <v>2</v>
       </c>
       <c r="D18" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F18" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G18" s="14">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H18" s="15">
-        <v>-47.058823529411</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="I18" s="14">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J18" s="14">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="K18" s="15">
-        <v>-47.5</v>
+        <v>-45.238095238095</v>
       </c>
       <c r="L18" s="15">
-        <v>-44.736842105263</v>
+        <v>-45.238095238095</v>
       </c>
       <c r="M18" s="15">
-        <v>-47.5</v>
+        <v>-47.727272727272</v>
       </c>
       <c r="N18" s="15">
-        <v>-92.579505300353</v>
+        <v>-92.459016393442</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D19" s="14">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E19" s="15">
-        <v>-33.333333333333</v>
+        <v>125</v>
       </c>
       <c r="F19" s="14">
+        <v>33</v>
+      </c>
+      <c r="G19" s="14">
         <v>32</v>
       </c>
-      <c r="G19" s="14">
-        <v>42</v>
-      </c>
       <c r="H19" s="15">
-        <v>-23.809523809523</v>
+        <v>3.125</v>
       </c>
       <c r="I19" s="14">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="J19" s="14">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="K19" s="15">
-        <v>2.985074626865</v>
+        <v>9.859154929577</v>
       </c>
       <c r="L19" s="15">
-        <v>-21.590909090909</v>
+        <v>-21.212121212121</v>
       </c>
       <c r="M19" s="15">
-        <v>-6.756756756756</v>
+        <v>-6.024096385542</v>
       </c>
       <c r="N19" s="15">
-        <v>-2.816901408450</v>
+        <v>-12.359550561797</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1107,31 +1107,31 @@
         <v>-20</v>
       </c>
       <c r="F20" s="14">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G20" s="14">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="H20" s="15">
-        <v>-54.838709677419</v>
+        <v>-40.740740740740</v>
       </c>
       <c r="I20" s="14">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="J20" s="14">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="K20" s="15">
-        <v>-31.481481481481</v>
+        <v>-30.508474576271</v>
       </c>
       <c r="L20" s="15">
-        <v>-9.756097560975</v>
+        <v>-4.651162790697</v>
       </c>
       <c r="M20" s="15">
-        <v>27.586206896551</v>
+        <v>28.125</v>
       </c>
       <c r="N20" s="15">
-        <v>-94.706723891273</v>
+        <v>-94.938271604938</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="D21" s="17">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E21" s="18">
-        <v>-27.272727272727</v>
+        <v>15</v>
       </c>
       <c r="F21" s="17">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="G21" s="17">
-        <v>123</v>
+        <v>103</v>
       </c>
       <c r="H21" s="18">
-        <v>-36.585365853658</v>
+        <v>-16.504854368932</v>
       </c>
       <c r="I21" s="17">
-        <v>167</v>
+        <v>190</v>
       </c>
       <c r="J21" s="17">
-        <v>216</v>
+        <v>236</v>
       </c>
       <c r="K21" s="18">
-        <v>-22.685185185185</v>
+        <v>-19.491525423728</v>
       </c>
       <c r="L21" s="18">
-        <v>-25.112107623318</v>
+        <v>-26.070038910505</v>
       </c>
       <c r="M21" s="18">
-        <v>-19.711538461538</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="N21" s="18">
-        <v>-86.629303442754</v>
+        <v>-86.619718309859</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="C22" s="14">
+        <v>2</v>
+      </c>
+      <c r="D22" s="14">
+        <v>1</v>
+      </c>
+      <c r="E22" s="15">
+        <v>100</v>
       </c>
       <c r="F22" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G22" s="14">
         <v>1</v>
       </c>
       <c r="H22" s="15">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="I22" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J22" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K22" s="15">
-        <v>350</v>
+        <v>266.666666666667</v>
       </c>
       <c r="L22" s="15">
-        <v>50</v>
+        <v>22.222222222222</v>
       </c>
       <c r="M22" s="15">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1224,31 +1224,31 @@
         <v>20</v>
       </c>
       <c r="D23" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E23" s="15">
         <v>-100</v>
       </c>
       <c r="F23" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G23" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H23" s="15">
-        <v>-50</v>
+        <v>-85.714285714285</v>
       </c>
       <c r="I23" s="14">
         <v>5</v>
       </c>
       <c r="J23" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K23" s="15">
-        <v>-16.666666666666</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="L23" s="15">
-        <v>-28.571428571428</v>
+        <v>-50</v>
       </c>
       <c r="M23" s="15">
         <v>-16.666666666666</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D24" s="14">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E24" s="15">
-        <v>29.411764705882</v>
+        <v>-30</v>
       </c>
       <c r="F24" s="14">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G24" s="14">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="H24" s="15">
-        <v>-22.105263157894</v>
+        <v>-16.470588235294</v>
       </c>
       <c r="I24" s="14">
-        <v>152</v>
+        <v>166</v>
       </c>
       <c r="J24" s="14">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="K24" s="15">
-        <v>8.571428571428</v>
+        <v>3.75</v>
       </c>
       <c r="L24" s="15">
-        <v>-7.878787878787</v>
+        <v>-12.169312169312</v>
       </c>
       <c r="M24" s="15">
-        <v>46.153846153846</v>
+        <v>45.614035087719</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D25" s="14">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E25" s="15">
-        <v>-66.666666666666</v>
+        <v>-77.777777777777</v>
       </c>
       <c r="F25" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G25" s="14">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="H25" s="15">
-        <v>-79.069767441860</v>
+        <v>-68.571428571428</v>
       </c>
       <c r="I25" s="14">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J25" s="14">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="K25" s="15">
-        <v>-55.555555555555</v>
+        <v>-58.730158730158</v>
       </c>
       <c r="L25" s="15">
-        <v>-67.567567567567</v>
+        <v>-69.047619047619</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D26" s="14">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E26" s="15">
-        <v>-26.666666666666</v>
+        <v>40</v>
       </c>
       <c r="F26" s="14">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G26" s="14">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="H26" s="15">
-        <v>-42.307692307692</v>
+        <v>-39.130434782608</v>
       </c>
       <c r="I26" s="14">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="J26" s="14">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="K26" s="15">
-        <v>-40.217391304347</v>
+        <v>-38.144329896907</v>
       </c>
       <c r="L26" s="15">
-        <v>-5.172413793103</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="M26" s="15">
-        <v>1.851851851851</v>
+        <v>0</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,32 +1387,32 @@
       <c r="C27" s="14">
         <v>1</v>
       </c>
-      <c r="D27" s="14">
-        <v>2</v>
-      </c>
-      <c r="E27" s="15">
-        <v>-50</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G27" s="14">
         <v>2</v>
       </c>
       <c r="H27" s="15">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I27" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J27" s="14">
         <v>3</v>
       </c>
       <c r="K27" s="15">
-        <v>66.666666666666</v>
+        <v>100</v>
       </c>
       <c r="L27" s="15">
-        <v>25</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,32 +1425,32 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>2</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D28" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E28" s="15">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="F28" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G28" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H28" s="15">
-        <v>25</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="I28" s="14">
         <v>11</v>
       </c>
       <c r="J28" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K28" s="15">
-        <v>57.142857142857</v>
+        <v>10</v>
       </c>
       <c r="L28" s="15">
         <v>57.142857142857</v>
@@ -1479,7 +1479,7 @@
         <v>20</v>
       </c>
       <c r="G29" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H29" s="15">
         <v>-100</v>
@@ -1520,7 +1520,7 @@
         <v>20</v>
       </c>
       <c r="G30" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H30" s="15">
         <v>-100</v>
@@ -1548,8 +1548,8 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="14">
-        <v>1</v>
+      <c r="C31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>
@@ -1560,11 +1560,11 @@
       <c r="F31" s="14">
         <v>2</v>
       </c>
-      <c r="G31" s="14">
-        <v>1</v>
-      </c>
-      <c r="H31" s="15">
-        <v>100</v>
+      <c r="G31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I31" s="14">
         <v>2</v>

--- a/data/source/weekly/cs-en-us-107pct.xlsx
+++ b/data/source/weekly/cs-en-us-107pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">9</t>
+      <t xml:space="preserve">10</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/23/2026</t>
+      <t xml:space="preserve">3/2/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/1/2026</t>
+      <t xml:space="preserve">3/8/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -893,7 +893,7 @@
         <v>22</v>
       </c>
       <c r="C15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -902,31 +902,31 @@
         <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G15" s="14">
         <v>1</v>
       </c>
       <c r="H15" s="15">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="I15" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J15" s="14">
         <v>2</v>
       </c>
       <c r="K15" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L15" s="15">
+        <v>20</v>
+      </c>
+      <c r="M15" s="15">
+        <v>200</v>
+      </c>
+      <c r="N15" s="15">
         <v>0</v>
-      </c>
-      <c r="M15" s="15">
-        <v>300</v>
-      </c>
-      <c r="N15" s="15">
-        <v>-33.333333333333</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D16" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E16" s="15">
-        <v>200</v>
+        <v>-50</v>
       </c>
       <c r="F16" s="14">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G16" s="14">
         <v>11</v>
       </c>
       <c r="H16" s="15">
-        <v>0</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="I16" s="14">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J16" s="14">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="K16" s="15">
-        <v>-5.263157894736</v>
+        <v>-13.043478260869</v>
       </c>
       <c r="L16" s="15">
-        <v>0</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="M16" s="15">
-        <v>-64.705882352941</v>
+        <v>-65.517241379310</v>
       </c>
       <c r="N16" s="15">
-        <v>-89.090909090909</v>
+        <v>-89.795918367346</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D17" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E17" s="15">
-        <v>-50</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="F17" s="14">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G17" s="14">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="H17" s="15">
-        <v>-22.222222222222</v>
+        <v>-45.833333333333</v>
       </c>
       <c r="I17" s="14">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J17" s="14">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="K17" s="15">
-        <v>-35</v>
+        <v>-40.425531914893</v>
       </c>
       <c r="L17" s="15">
-        <v>-48</v>
+        <v>-49.090909090909</v>
       </c>
       <c r="M17" s="15">
-        <v>62.5</v>
+        <v>64.705882352941</v>
       </c>
       <c r="N17" s="15">
-        <v>-40.909090909090</v>
+        <v>-39.130434782608</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D18" s="14">
         <v>2</v>
       </c>
       <c r="E18" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F18" s="14">
+        <v>9</v>
+      </c>
+      <c r="G18" s="14">
         <v>10</v>
       </c>
-      <c r="G18" s="14">
-        <v>13</v>
-      </c>
       <c r="H18" s="15">
-        <v>-23.076923076923</v>
+        <v>-10</v>
       </c>
       <c r="I18" s="14">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J18" s="14">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K18" s="15">
-        <v>-45.238095238095</v>
+        <v>-40.909090909090</v>
       </c>
       <c r="L18" s="15">
-        <v>-45.238095238095</v>
+        <v>-43.478260869565</v>
       </c>
       <c r="M18" s="15">
-        <v>-47.727272727272</v>
+        <v>-44.680851063829</v>
       </c>
       <c r="N18" s="15">
-        <v>-92.459016393442</v>
+        <v>-92.073170731707</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D19" s="14">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E19" s="15">
-        <v>125</v>
+        <v>87.5</v>
       </c>
       <c r="F19" s="14">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="G19" s="14">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H19" s="15">
-        <v>3.125</v>
+        <v>25.806451612903</v>
       </c>
       <c r="I19" s="14">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="J19" s="14">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="K19" s="15">
-        <v>9.859154929577</v>
+        <v>18.987341772151</v>
       </c>
       <c r="L19" s="15">
-        <v>-21.212121212121</v>
+        <v>-16.814159292035</v>
       </c>
       <c r="M19" s="15">
-        <v>-6.024096385542</v>
+        <v>1.075268817204</v>
       </c>
       <c r="N19" s="15">
-        <v>-12.359550561797</v>
+        <v>-1.052631578947</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
+        <v>10</v>
+      </c>
+      <c r="D20" s="14">
         <v>4</v>
       </c>
-      <c r="D20" s="14">
-        <v>5</v>
-      </c>
       <c r="E20" s="15">
-        <v>-20</v>
+        <v>150</v>
       </c>
       <c r="F20" s="14">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="G20" s="14">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="H20" s="15">
-        <v>-40.740740740740</v>
+        <v>9.523809523809</v>
       </c>
       <c r="I20" s="14">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="J20" s="14">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="K20" s="15">
-        <v>-30.508474576271</v>
+        <v>-19.047619047619</v>
       </c>
       <c r="L20" s="15">
-        <v>-4.651162790697</v>
+        <v>0</v>
       </c>
       <c r="M20" s="15">
-        <v>28.125</v>
+        <v>54.545454545454</v>
       </c>
       <c r="N20" s="15">
-        <v>-94.938271604938</v>
+        <v>-94.333333333333</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="D21" s="17">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E21" s="18">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="F21" s="17">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="G21" s="17">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="H21" s="18">
-        <v>-16.504854368932</v>
+        <v>-1.010101010101</v>
       </c>
       <c r="I21" s="17">
-        <v>190</v>
+        <v>225</v>
       </c>
       <c r="J21" s="17">
-        <v>236</v>
+        <v>261</v>
       </c>
       <c r="K21" s="18">
-        <v>-19.491525423728</v>
+        <v>-13.793103448275</v>
       </c>
       <c r="L21" s="18">
-        <v>-26.070038910505</v>
+        <v>-23.208191126279</v>
       </c>
       <c r="M21" s="18">
-        <v>-16.666666666666</v>
+        <v>-10.358565737051</v>
       </c>
       <c r="N21" s="18">
-        <v>-86.619718309859</v>
+        <v>-85.696122059758</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,37 +1180,37 @@
         <v>29</v>
       </c>
       <c r="C22" s="14">
+        <v>1</v>
+      </c>
+      <c r="D22" s="14">
         <v>2</v>
       </c>
-      <c r="D22" s="14">
-        <v>1</v>
-      </c>
       <c r="E22" s="15">
+        <v>-50</v>
+      </c>
+      <c r="F22" s="14">
+        <v>6</v>
+      </c>
+      <c r="G22" s="14">
+        <v>3</v>
+      </c>
+      <c r="H22" s="15">
         <v>100</v>
       </c>
-      <c r="F22" s="14">
-        <v>7</v>
-      </c>
-      <c r="G22" s="14">
-        <v>1</v>
-      </c>
-      <c r="H22" s="15">
-        <v>600</v>
-      </c>
       <c r="I22" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J22" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K22" s="15">
-        <v>266.666666666667</v>
+        <v>140</v>
       </c>
       <c r="L22" s="15">
-        <v>22.222222222222</v>
+        <v>9.090909090909</v>
       </c>
       <c r="M22" s="15">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
+      <c r="C23" s="14">
+        <v>1</v>
       </c>
       <c r="D23" s="14">
+        <v>5</v>
+      </c>
+      <c r="E23" s="15">
+        <v>-80</v>
+      </c>
+      <c r="F23" s="14">
         <v>3</v>
       </c>
-      <c r="E23" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F23" s="14">
-        <v>1</v>
-      </c>
       <c r="G23" s="14">
+        <v>11</v>
+      </c>
+      <c r="H23" s="15">
+        <v>-72.727272727272</v>
+      </c>
+      <c r="I23" s="14">
         <v>7</v>
       </c>
-      <c r="H23" s="15">
-        <v>-85.714285714285</v>
-      </c>
-      <c r="I23" s="14">
-        <v>5</v>
-      </c>
       <c r="J23" s="14">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="K23" s="15">
-        <v>-44.444444444444</v>
+        <v>-50</v>
       </c>
       <c r="L23" s="15">
-        <v>-50</v>
+        <v>-30</v>
       </c>
       <c r="M23" s="15">
-        <v>-16.666666666666</v>
+        <v>0</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D24" s="14">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E24" s="15">
-        <v>-30</v>
+        <v>11.111111111111</v>
       </c>
       <c r="F24" s="14">
+        <v>76</v>
+      </c>
+      <c r="G24" s="14">
         <v>71</v>
       </c>
-      <c r="G24" s="14">
-        <v>85</v>
-      </c>
       <c r="H24" s="15">
-        <v>-16.470588235294</v>
+        <v>7.042253521126</v>
       </c>
       <c r="I24" s="14">
-        <v>166</v>
+        <v>185</v>
       </c>
       <c r="J24" s="14">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="K24" s="15">
-        <v>3.75</v>
+        <v>3.932584269662</v>
       </c>
       <c r="L24" s="15">
-        <v>-12.169312169312</v>
+        <v>-13.145539906103</v>
       </c>
       <c r="M24" s="15">
-        <v>45.614035087719</v>
+        <v>48</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
+        <v>5</v>
+      </c>
+      <c r="D25" s="14">
         <v>2</v>
       </c>
-      <c r="D25" s="14">
-        <v>9</v>
-      </c>
       <c r="E25" s="15">
-        <v>-77.777777777777</v>
+        <v>150</v>
       </c>
       <c r="F25" s="14">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G25" s="14">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="H25" s="15">
-        <v>-68.571428571428</v>
+        <v>-26.315789473684</v>
       </c>
       <c r="I25" s="14">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="J25" s="14">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="K25" s="15">
-        <v>-58.730158730158</v>
+        <v>-52.307692307692</v>
       </c>
       <c r="L25" s="15">
-        <v>-69.047619047619</v>
+        <v>-67.021276595744</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="D26" s="14">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E26" s="15">
-        <v>40</v>
+        <v>61.538461538461</v>
       </c>
       <c r="F26" s="14">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="G26" s="14">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H26" s="15">
-        <v>-39.130434782608</v>
+        <v>-2.325581395348</v>
       </c>
       <c r="I26" s="14">
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="J26" s="14">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="K26" s="15">
-        <v>-38.144329896907</v>
+        <v>-26.363636363636</v>
       </c>
       <c r="L26" s="15">
-        <v>-14.285714285714</v>
+        <v>1.25</v>
       </c>
       <c r="M26" s="15">
-        <v>0</v>
+        <v>9.459459459459</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,7 +1385,7 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1403,16 +1403,16 @@
         <v>100</v>
       </c>
       <c r="I27" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J27" s="14">
         <v>3</v>
       </c>
       <c r="K27" s="15">
-        <v>100</v>
+        <v>166.666666666667</v>
       </c>
       <c r="L27" s="15">
-        <v>-14.285714285714</v>
+        <v>0</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,20 +1428,20 @@
       <c r="C28" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D28" s="14">
-        <v>3</v>
-      </c>
-      <c r="E28" s="15">
-        <v>-100</v>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
         <v>4</v>
       </c>
       <c r="G28" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H28" s="15">
-        <v>-42.857142857142</v>
+        <v>-20</v>
       </c>
       <c r="I28" s="14">
         <v>11</v>
@@ -1453,7 +1453,7 @@
         <v>10</v>
       </c>
       <c r="L28" s="15">
-        <v>57.142857142857</v>
+        <v>37.5</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1558,7 +1558,7 @@
         <v>21</v>
       </c>
       <c r="F31" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
@@ -1567,13 +1567,13 @@
         <v>21</v>
       </c>
       <c r="I31" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J31" s="14">
         <v>3</v>
       </c>
       <c r="K31" s="15">
-        <v>-33.333333333333</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-107pct.xlsx
+++ b/data/source/weekly/cs-en-us-107pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">11</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/2/2026</t>
+      <t xml:space="preserve">3/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/8/2026</t>
+      <t xml:space="preserve">3/15/2026</t>
     </r>
   </si>
   <si>
@@ -692,10 +692,10 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -851,8 +851,8 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>20</v>
+      <c r="C14" s="14">
+        <v>1</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>20</v>
@@ -860,32 +860,32 @@
       <c r="E14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G14" s="14">
+      <c r="F14" s="14">
         <v>1</v>
       </c>
-      <c r="H14" s="15">
-        <v>-100</v>
-      </c>
-      <c r="I14" s="13" t="s">
-        <v>20</v>
+      <c r="G14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="I14" s="14">
+        <v>1</v>
       </c>
       <c r="J14" s="14">
         <v>3</v>
       </c>
       <c r="K14" s="15">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L14" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M14" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="N14" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -902,31 +902,31 @@
         <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G15" s="14">
         <v>1</v>
       </c>
       <c r="H15" s="15">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="I15" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J15" s="14">
         <v>2</v>
       </c>
       <c r="K15" s="15">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="L15" s="15">
-        <v>20</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M15" s="15">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="N15" s="15">
-        <v>0</v>
+        <v>14.285714285714</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,37 +937,37 @@
         <v>2</v>
       </c>
       <c r="D16" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E16" s="15">
-        <v>-50</v>
+        <v>100</v>
       </c>
       <c r="F16" s="14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G16" s="14">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H16" s="15">
-        <v>-9.090909090909</v>
+        <v>-12.5</v>
       </c>
       <c r="I16" s="14">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J16" s="14">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K16" s="15">
-        <v>-13.043478260869</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="L16" s="15">
-        <v>-9.090909090909</v>
+        <v>0</v>
       </c>
       <c r="M16" s="15">
-        <v>-65.517241379310</v>
+        <v>-64.516129032258</v>
       </c>
       <c r="N16" s="15">
-        <v>-89.795918367346</v>
+        <v>-89.861751152073</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D17" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E17" s="15">
-        <v>-71.428571428571</v>
+        <v>40</v>
       </c>
       <c r="F17" s="14">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="G17" s="14">
         <v>24</v>
       </c>
       <c r="H17" s="15">
-        <v>-45.833333333333</v>
+        <v>-25</v>
       </c>
       <c r="I17" s="14">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="J17" s="14">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="K17" s="15">
-        <v>-40.425531914893</v>
+        <v>-32.692307692307</v>
       </c>
       <c r="L17" s="15">
-        <v>-49.090909090909</v>
+        <v>-45.3125</v>
       </c>
       <c r="M17" s="15">
-        <v>64.705882352941</v>
+        <v>94.444444444444</v>
       </c>
       <c r="N17" s="15">
-        <v>-39.130434782608</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D18" s="14">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E18" s="15">
+        <v>-66.666666666666</v>
+      </c>
+      <c r="F18" s="14">
+        <v>7</v>
+      </c>
+      <c r="G18" s="14">
+        <v>11</v>
+      </c>
+      <c r="H18" s="15">
+        <v>-36.363636363636</v>
+      </c>
+      <c r="I18" s="14">
+        <v>28</v>
+      </c>
+      <c r="J18" s="14">
         <v>50</v>
       </c>
-      <c r="F18" s="14">
-        <v>9</v>
-      </c>
-      <c r="G18" s="14">
-        <v>10</v>
-      </c>
-      <c r="H18" s="15">
-        <v>-10</v>
-      </c>
-      <c r="I18" s="14">
-        <v>26</v>
-      </c>
-      <c r="J18" s="14">
-        <v>44</v>
-      </c>
       <c r="K18" s="15">
-        <v>-40.909090909090</v>
+        <v>-44</v>
       </c>
       <c r="L18" s="15">
-        <v>-43.478260869565</v>
+        <v>-40.425531914893</v>
       </c>
       <c r="M18" s="15">
-        <v>-44.680851063829</v>
+        <v>-47.169811320754</v>
       </c>
       <c r="N18" s="15">
-        <v>-92.073170731707</v>
+        <v>-92</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D19" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E19" s="15">
-        <v>87.5</v>
+        <v>40</v>
       </c>
       <c r="F19" s="14">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="G19" s="14">
         <v>31</v>
       </c>
       <c r="H19" s="15">
-        <v>25.806451612903</v>
+        <v>45.161290322580</v>
       </c>
       <c r="I19" s="14">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="J19" s="14">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="K19" s="15">
-        <v>18.987341772151</v>
+        <v>21.348314606741</v>
       </c>
       <c r="L19" s="15">
-        <v>-16.814159292035</v>
+        <v>-10.743801652892</v>
       </c>
       <c r="M19" s="15">
-        <v>1.075268817204</v>
+        <v>8</v>
       </c>
       <c r="N19" s="15">
-        <v>-1.052631578947</v>
+        <v>1.886792452830</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D20" s="14">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E20" s="15">
-        <v>150</v>
+        <v>-37.5</v>
       </c>
       <c r="F20" s="14">
         <v>23</v>
       </c>
       <c r="G20" s="14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H20" s="15">
-        <v>9.523809523809</v>
+        <v>4.545454545454</v>
       </c>
       <c r="I20" s="14">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="J20" s="14">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="K20" s="15">
-        <v>-19.047619047619</v>
+        <v>-21.126760563380</v>
       </c>
       <c r="L20" s="15">
-        <v>0</v>
+        <v>3.703703703703</v>
       </c>
       <c r="M20" s="15">
-        <v>54.545454545454</v>
+        <v>55.555555555555</v>
       </c>
       <c r="N20" s="15">
-        <v>-94.333333333333</v>
+        <v>-94.303153611393</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,63 +1139,63 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D21" s="17">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E21" s="18">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="F21" s="17">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="G21" s="17">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="H21" s="18">
-        <v>-1.010101010101</v>
+        <v>10.309278350515</v>
       </c>
       <c r="I21" s="17">
-        <v>225</v>
+        <v>258</v>
       </c>
       <c r="J21" s="17">
-        <v>261</v>
+        <v>291</v>
       </c>
       <c r="K21" s="18">
-        <v>-13.793103448275</v>
+        <v>-11.340206185567</v>
       </c>
       <c r="L21" s="18">
-        <v>-23.208191126279</v>
+        <v>-18.095238095238</v>
       </c>
       <c r="M21" s="18">
-        <v>-10.358565737051</v>
+        <v>-5.147058823529</v>
       </c>
       <c r="N21" s="18">
-        <v>-85.696122059758</v>
+        <v>-84.956268221574</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>1</v>
-      </c>
-      <c r="D22" s="14">
-        <v>2</v>
-      </c>
-      <c r="E22" s="15">
-        <v>-50</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G22" s="14">
         <v>3</v>
       </c>
       <c r="H22" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I22" s="14">
         <v>12</v>
@@ -1207,10 +1207,10 @@
         <v>140</v>
       </c>
       <c r="L22" s="15">
-        <v>9.090909090909</v>
+        <v>0</v>
       </c>
       <c r="M22" s="15">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,32 +1220,32 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="14">
+      <c r="C23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" s="14">
         <v>1</v>
       </c>
-      <c r="D23" s="14">
-        <v>5</v>
-      </c>
       <c r="E23" s="15">
-        <v>-80</v>
+        <v>-100</v>
       </c>
       <c r="F23" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G23" s="14">
         <v>11</v>
       </c>
       <c r="H23" s="15">
-        <v>-72.727272727272</v>
+        <v>-81.818181818181</v>
       </c>
       <c r="I23" s="14">
         <v>7</v>
       </c>
       <c r="J23" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K23" s="15">
-        <v>-50</v>
+        <v>-53.333333333333</v>
       </c>
       <c r="L23" s="15">
         <v>-30</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D24" s="14">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E24" s="15">
-        <v>11.111111111111</v>
+        <v>13.636363636363</v>
       </c>
       <c r="F24" s="14">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="G24" s="14">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="H24" s="15">
-        <v>7.042253521126</v>
+        <v>3.896103896103</v>
       </c>
       <c r="I24" s="14">
-        <v>185</v>
+        <v>210</v>
       </c>
       <c r="J24" s="14">
-        <v>178</v>
+        <v>200</v>
       </c>
       <c r="K24" s="15">
-        <v>3.932584269662</v>
+        <v>5</v>
       </c>
       <c r="L24" s="15">
-        <v>-13.145539906103</v>
+        <v>-11.016949152542</v>
       </c>
       <c r="M24" s="15">
-        <v>48</v>
+        <v>48.936170212766</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D25" s="14">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E25" s="15">
-        <v>150</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F25" s="14">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G25" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H25" s="15">
-        <v>-26.315789473684</v>
+        <v>-20</v>
       </c>
       <c r="I25" s="14">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="J25" s="14">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="K25" s="15">
-        <v>-52.307692307692</v>
+        <v>-45.070422535211</v>
       </c>
       <c r="L25" s="15">
-        <v>-67.021276595744</v>
+        <v>-61.764705882352</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D26" s="14">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E26" s="15">
-        <v>61.538461538461</v>
+        <v>180</v>
       </c>
       <c r="F26" s="14">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="G26" s="14">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H26" s="15">
-        <v>-2.325581395348</v>
+        <v>36.842105263157</v>
       </c>
       <c r="I26" s="14">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="J26" s="14">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="K26" s="15">
-        <v>-26.363636363636</v>
+        <v>-17.391304347826</v>
       </c>
       <c r="L26" s="15">
-        <v>1.25</v>
+        <v>6.741573033707</v>
       </c>
       <c r="M26" s="15">
-        <v>9.459459459459</v>
+        <v>15.853658536585</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,7 +1385,7 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1394,25 +1394,25 @@
         <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G27" s="14">
         <v>2</v>
       </c>
       <c r="H27" s="15">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="I27" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J27" s="14">
         <v>3</v>
       </c>
       <c r="K27" s="15">
-        <v>166.666666666667</v>
+        <v>266.666666666667</v>
       </c>
       <c r="L27" s="15">
-        <v>0</v>
+        <v>22.222222222222</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="C28" s="14">
+        <v>6</v>
+      </c>
+      <c r="D28" s="14">
+        <v>2</v>
+      </c>
+      <c r="E28" s="15">
+        <v>200</v>
       </c>
       <c r="F28" s="14">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G28" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H28" s="15">
-        <v>-20</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I28" s="14">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="J28" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K28" s="15">
-        <v>10</v>
+        <v>41.666666666666</v>
       </c>
       <c r="L28" s="15">
-        <v>37.5</v>
+        <v>112.5</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1478,11 +1478,11 @@
       <c r="F29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G29" s="14">
-        <v>1</v>
-      </c>
-      <c r="H29" s="15">
-        <v>-100</v>
+      <c r="G29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I29" s="13" t="s">
         <v>20</v>
@@ -1519,11 +1519,11 @@
       <c r="F30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G30" s="14">
-        <v>1</v>
-      </c>
-      <c r="H30" s="15">
-        <v>-100</v>
+      <c r="G30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I30" s="13" t="s">
         <v>20</v>
@@ -1558,7 +1558,7 @@
         <v>21</v>
       </c>
       <c r="F31" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-107pct.xlsx
+++ b/data/source/weekly/cs-en-us-107pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">12</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/9/2026</t>
+      <t xml:space="preserve">3/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/15/2026</t>
+      <t xml:space="preserve">3/22/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
@@ -851,8 +851,8 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="14">
-        <v>1</v>
+      <c r="C14" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>20</v>
@@ -892,8 +892,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>2</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -902,13 +902,13 @@
         <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>6</v>
-      </c>
-      <c r="G15" s="14">
-        <v>1</v>
-      </c>
-      <c r="H15" s="15">
-        <v>500</v>
+        <v>5</v>
+      </c>
+      <c r="G15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I15" s="14">
         <v>8</v>
@@ -920,13 +920,13 @@
         <v>300</v>
       </c>
       <c r="L15" s="15">
-        <v>33.333333333333</v>
+        <v>14.285714285714</v>
       </c>
       <c r="M15" s="15">
         <v>300</v>
       </c>
       <c r="N15" s="15">
-        <v>14.285714285714</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D16" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E16" s="15">
-        <v>100</v>
+        <v>-75</v>
       </c>
       <c r="F16" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G16" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H16" s="15">
-        <v>-12.5</v>
+        <v>-10</v>
       </c>
       <c r="I16" s="14">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J16" s="14">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="K16" s="15">
-        <v>-8.333333333333</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="L16" s="15">
-        <v>0</v>
+        <v>4.347826086956</v>
       </c>
       <c r="M16" s="15">
-        <v>-64.516129032258</v>
+        <v>-61.904761904761</v>
       </c>
       <c r="N16" s="15">
-        <v>-89.861751152073</v>
+        <v>-89.565217391304</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D17" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E17" s="15">
+        <v>-33.333333333333</v>
+      </c>
+      <c r="F17" s="14">
+        <v>17</v>
+      </c>
+      <c r="G17" s="14">
+        <v>26</v>
+      </c>
+      <c r="H17" s="15">
+        <v>-34.615384615384</v>
+      </c>
+      <c r="I17" s="14">
         <v>40</v>
       </c>
-      <c r="F17" s="14">
-        <v>18</v>
-      </c>
-      <c r="G17" s="14">
-        <v>24</v>
-      </c>
-      <c r="H17" s="15">
-        <v>-25</v>
-      </c>
-      <c r="I17" s="14">
-        <v>35</v>
-      </c>
       <c r="J17" s="14">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="K17" s="15">
-        <v>-32.692307692307</v>
+        <v>-31.034482758620</v>
       </c>
       <c r="L17" s="15">
-        <v>-45.3125</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="M17" s="15">
-        <v>94.444444444444</v>
+        <v>122.222222222222</v>
       </c>
       <c r="N17" s="15">
-        <v>-30</v>
+        <v>-28.571428571428</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1025,31 +1025,31 @@
         <v>-66.666666666666</v>
       </c>
       <c r="F18" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G18" s="14">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H18" s="15">
-        <v>-36.363636363636</v>
+        <v>-43.75</v>
       </c>
       <c r="I18" s="14">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J18" s="14">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="K18" s="15">
-        <v>-44</v>
+        <v>-46.428571428571</v>
       </c>
       <c r="L18" s="15">
-        <v>-40.425531914893</v>
+        <v>-41.176470588235</v>
       </c>
       <c r="M18" s="15">
-        <v>-47.169811320754</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="N18" s="15">
-        <v>-92</v>
+        <v>-91.758241758241</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,37 +1060,37 @@
         <v>14</v>
       </c>
       <c r="D19" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E19" s="15">
-        <v>40</v>
+        <v>7.692307692307</v>
       </c>
       <c r="F19" s="14">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="G19" s="14">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H19" s="15">
-        <v>45.161290322580</v>
+        <v>45.714285714285</v>
       </c>
       <c r="I19" s="14">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="J19" s="14">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="K19" s="15">
-        <v>21.348314606741</v>
+        <v>18.627450980392</v>
       </c>
       <c r="L19" s="15">
-        <v>-10.743801652892</v>
+        <v>-12.318840579710</v>
       </c>
       <c r="M19" s="15">
-        <v>8</v>
+        <v>17.475728155339</v>
       </c>
       <c r="N19" s="15">
-        <v>1.886792452830</v>
+        <v>5.217391304347</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D20" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E20" s="15">
-        <v>-37.5</v>
+        <v>116.666666666667</v>
       </c>
       <c r="F20" s="14">
+        <v>32</v>
+      </c>
+      <c r="G20" s="14">
         <v>23</v>
       </c>
-      <c r="G20" s="14">
-        <v>22</v>
-      </c>
       <c r="H20" s="15">
-        <v>4.545454545454</v>
+        <v>39.130434782608</v>
       </c>
       <c r="I20" s="14">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="J20" s="14">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="K20" s="15">
-        <v>-21.126760563380</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="L20" s="15">
-        <v>3.703703703703</v>
+        <v>12.903225806451</v>
       </c>
       <c r="M20" s="15">
-        <v>55.555555555555</v>
+        <v>66.666666666666</v>
       </c>
       <c r="N20" s="15">
-        <v>-94.303153611393</v>
+        <v>-93.383742911153</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D21" s="17">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E21" s="18">
-        <v>10</v>
+        <v>-2.857142857142</v>
       </c>
       <c r="F21" s="17">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="G21" s="17">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="H21" s="18">
-        <v>10.309278350515</v>
+        <v>12.727272727272</v>
       </c>
       <c r="I21" s="17">
-        <v>258</v>
+        <v>294</v>
       </c>
       <c r="J21" s="17">
-        <v>291</v>
+        <v>326</v>
       </c>
       <c r="K21" s="18">
-        <v>-11.340206185567</v>
+        <v>-9.815950920245</v>
       </c>
       <c r="L21" s="18">
-        <v>-18.095238095238</v>
+        <v>-15.273775216138</v>
       </c>
       <c r="M21" s="18">
-        <v>-5.147058823529</v>
+        <v>3.521126760563</v>
       </c>
       <c r="N21" s="18">
-        <v>-84.956268221574</v>
+        <v>-83.960720130932</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1220,35 +1220,35 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
+      <c r="C23" s="14">
+        <v>1</v>
       </c>
       <c r="D23" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E23" s="15">
-        <v>-100</v>
+        <v>-75</v>
       </c>
       <c r="F23" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G23" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H23" s="15">
-        <v>-81.818181818181</v>
+        <v>-76.923076923076</v>
       </c>
       <c r="I23" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J23" s="14">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="K23" s="15">
-        <v>-53.333333333333</v>
+        <v>-57.894736842105</v>
       </c>
       <c r="L23" s="15">
-        <v>-30</v>
+        <v>-20</v>
       </c>
       <c r="M23" s="15">
         <v>0</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="D24" s="14">
         <v>22</v>
       </c>
       <c r="E24" s="15">
-        <v>13.636363636363</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="F24" s="14">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="G24" s="14">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H24" s="15">
-        <v>3.896103896103</v>
+        <v>-14.634146341463</v>
       </c>
       <c r="I24" s="14">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="J24" s="14">
-        <v>200</v>
+        <v>222</v>
       </c>
       <c r="K24" s="15">
-        <v>5</v>
+        <v>-0.900900900900</v>
       </c>
       <c r="L24" s="15">
-        <v>-11.016949152542</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="M24" s="15">
-        <v>48.936170212766</v>
+        <v>42.857142857142</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
+        <v>4</v>
+      </c>
+      <c r="D25" s="14">
         <v>8</v>
       </c>
-      <c r="D25" s="14">
-        <v>6</v>
-      </c>
       <c r="E25" s="15">
-        <v>33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="F25" s="14">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G25" s="14">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H25" s="15">
-        <v>-20</v>
+        <v>-28</v>
       </c>
       <c r="I25" s="14">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J25" s="14">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="K25" s="15">
-        <v>-45.070422535211</v>
+        <v>-46.835443037974</v>
       </c>
       <c r="L25" s="15">
-        <v>-61.764705882352</v>
+        <v>-63.793103448275</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
+        <v>8</v>
+      </c>
+      <c r="D26" s="14">
         <v>14</v>
       </c>
-      <c r="D26" s="14">
-        <v>5</v>
-      </c>
       <c r="E26" s="15">
-        <v>180</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="F26" s="14">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G26" s="14">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H26" s="15">
-        <v>36.842105263157</v>
+        <v>35.135135135135</v>
       </c>
       <c r="I26" s="14">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="J26" s="14">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="K26" s="15">
-        <v>-17.391304347826</v>
+        <v>-20.930232558139</v>
       </c>
       <c r="L26" s="15">
-        <v>6.741573033707</v>
+        <v>6.25</v>
       </c>
       <c r="M26" s="15">
-        <v>15.853658536585</v>
+        <v>14.606741573033</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>3</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1394,13 +1394,13 @@
         <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>7</v>
-      </c>
-      <c r="G27" s="14">
-        <v>2</v>
-      </c>
-      <c r="H27" s="15">
-        <v>250</v>
+        <v>6</v>
+      </c>
+      <c r="G27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I27" s="14">
         <v>11</v>
@@ -1412,7 +1412,7 @@
         <v>266.666666666667</v>
       </c>
       <c r="L27" s="15">
-        <v>22.222222222222</v>
+        <v>10</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D28" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E28" s="15">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="F28" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G28" s="14">
         <v>6</v>
       </c>
       <c r="H28" s="15">
-        <v>33.333333333333</v>
+        <v>83.333333333333</v>
       </c>
       <c r="I28" s="14">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J28" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K28" s="15">
-        <v>41.666666666666</v>
+        <v>61.538461538461</v>
       </c>
       <c r="L28" s="15">
-        <v>112.5</v>
+        <v>162.5</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1575,8 +1575,8 @@
       <c r="K31" s="15">
         <v>33.333333333333</v>
       </c>
-      <c r="L31" s="13" t="s">
-        <v>21</v>
+      <c r="L31" s="15">
+        <v>300</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-107pct.xlsx
+++ b/data/source/weekly/cs-en-us-107pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve">13</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/16/2026</t>
+      <t xml:space="preserve">3/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/22/2026</t>
+      <t xml:space="preserve">3/29/2026</t>
     </r>
   </si>
   <si>
@@ -892,41 +892,41 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="C15" s="14">
+        <v>2</v>
+      </c>
+      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>100</v>
       </c>
       <c r="F15" s="14">
-        <v>5</v>
-      </c>
-      <c r="G15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>21</v>
+        <v>6</v>
+      </c>
+      <c r="G15" s="14">
+        <v>1</v>
+      </c>
+      <c r="H15" s="15">
+        <v>500</v>
       </c>
       <c r="I15" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J15" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K15" s="15">
-        <v>300</v>
+        <v>233.333333333333</v>
       </c>
       <c r="L15" s="15">
-        <v>14.285714285714</v>
+        <v>42.857142857142</v>
       </c>
       <c r="M15" s="15">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="N15" s="15">
-        <v>0</v>
+        <v>11.111111111111</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D16" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E16" s="15">
-        <v>-75</v>
+        <v>50</v>
       </c>
       <c r="F16" s="14">
         <v>9</v>
       </c>
       <c r="G16" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H16" s="15">
-        <v>-10</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="I16" s="14">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J16" s="14">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K16" s="15">
-        <v>-14.285714285714</v>
+        <v>-6.666666666666</v>
       </c>
       <c r="L16" s="15">
-        <v>4.347826086956</v>
+        <v>0</v>
       </c>
       <c r="M16" s="15">
-        <v>-61.904761904761</v>
+        <v>-58.208955223880</v>
       </c>
       <c r="N16" s="15">
-        <v>-89.565217391304</v>
+        <v>-88.333333333333</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D17" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E17" s="15">
+        <v>-40</v>
+      </c>
+      <c r="F17" s="14">
+        <v>15</v>
+      </c>
+      <c r="G17" s="14">
+        <v>23</v>
+      </c>
+      <c r="H17" s="15">
+        <v>-34.782608695652</v>
+      </c>
+      <c r="I17" s="14">
+        <v>42</v>
+      </c>
+      <c r="J17" s="14">
+        <v>63</v>
+      </c>
+      <c r="K17" s="15">
         <v>-33.333333333333</v>
       </c>
-      <c r="F17" s="14">
-        <v>17</v>
-      </c>
-      <c r="G17" s="14">
-        <v>26</v>
-      </c>
-      <c r="H17" s="15">
-        <v>-34.615384615384</v>
-      </c>
-      <c r="I17" s="14">
-        <v>40</v>
-      </c>
-      <c r="J17" s="14">
-        <v>58</v>
-      </c>
-      <c r="K17" s="15">
-        <v>-31.034482758620</v>
-      </c>
       <c r="L17" s="15">
-        <v>-38.461538461538</v>
+        <v>-39.130434782608</v>
       </c>
       <c r="M17" s="15">
-        <v>122.222222222222</v>
+        <v>110</v>
       </c>
       <c r="N17" s="15">
-        <v>-28.571428571428</v>
+        <v>-27.586206896551</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D18" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E18" s="15">
-        <v>-66.666666666666</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="F18" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G18" s="14">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="H18" s="15">
-        <v>-43.75</v>
+        <v>-47.619047619047</v>
       </c>
       <c r="I18" s="14">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="J18" s="14">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="K18" s="15">
-        <v>-46.428571428571</v>
+        <v>-46.031746031746</v>
       </c>
       <c r="L18" s="15">
-        <v>-41.176470588235</v>
+        <v>-38.181818181818</v>
       </c>
       <c r="M18" s="15">
-        <v>-45.454545454545</v>
+        <v>-43.333333333333</v>
       </c>
       <c r="N18" s="15">
-        <v>-91.758241758241</v>
+        <v>-91.168831168831</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D19" s="14">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E19" s="15">
-        <v>7.692307692307</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F19" s="14">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G19" s="14">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H19" s="15">
-        <v>45.714285714285</v>
+        <v>32.5</v>
       </c>
       <c r="I19" s="14">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="J19" s="14">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="K19" s="15">
-        <v>18.627450980392</v>
+        <v>20.720720720720</v>
       </c>
       <c r="L19" s="15">
-        <v>-12.318840579710</v>
+        <v>-7.586206896551</v>
       </c>
       <c r="M19" s="15">
-        <v>17.475728155339</v>
+        <v>15.517241379310</v>
       </c>
       <c r="N19" s="15">
-        <v>5.217391304347</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D20" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E20" s="15">
-        <v>116.666666666667</v>
+        <v>-37.5</v>
       </c>
       <c r="F20" s="14">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G20" s="14">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="H20" s="15">
-        <v>39.130434782608</v>
+        <v>26.923076923076</v>
       </c>
       <c r="I20" s="14">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="J20" s="14">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="K20" s="15">
-        <v>-9.090909090909</v>
+        <v>-12.941176470588</v>
       </c>
       <c r="L20" s="15">
-        <v>12.903225806451</v>
+        <v>1.369863013698</v>
       </c>
       <c r="M20" s="15">
-        <v>66.666666666666</v>
+        <v>60.869565217391</v>
       </c>
       <c r="N20" s="15">
-        <v>-93.383742911153</v>
+        <v>-93.626184323858</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D21" s="17">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E21" s="18">
-        <v>-2.857142857142</v>
+        <v>-9.375</v>
       </c>
       <c r="F21" s="17">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G21" s="17">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="H21" s="18">
-        <v>12.727272727272</v>
+        <v>4.918032786885</v>
       </c>
       <c r="I21" s="17">
-        <v>294</v>
+        <v>323</v>
       </c>
       <c r="J21" s="17">
-        <v>326</v>
+        <v>358</v>
       </c>
       <c r="K21" s="18">
-        <v>-9.815950920245</v>
+        <v>-9.776536312849</v>
       </c>
       <c r="L21" s="18">
-        <v>-15.273775216138</v>
+        <v>-14.550264550264</v>
       </c>
       <c r="M21" s="18">
-        <v>3.521126760563</v>
+        <v>3.525641025641</v>
       </c>
       <c r="N21" s="18">
-        <v>-83.960720130932</v>
+        <v>-83.686868686868</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="14">
+        <v>1</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1189,28 +1189,28 @@
         <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G22" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H22" s="15">
         <v>0</v>
       </c>
       <c r="I22" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J22" s="14">
         <v>5</v>
       </c>
       <c r="K22" s="15">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="L22" s="15">
         <v>0</v>
       </c>
       <c r="M22" s="15">
-        <v>100</v>
+        <v>116.666666666667</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,23 +1220,23 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="14">
-        <v>1</v>
-      </c>
-      <c r="D23" s="14">
-        <v>4</v>
-      </c>
-      <c r="E23" s="15">
-        <v>-75</v>
+      <c r="C23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F23" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G23" s="14">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H23" s="15">
-        <v>-76.923076923076</v>
+        <v>-80</v>
       </c>
       <c r="I23" s="14">
         <v>8</v>
@@ -1248,7 +1248,7 @@
         <v>-57.894736842105</v>
       </c>
       <c r="L23" s="15">
-        <v>-20</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M23" s="15">
         <v>0</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D24" s="14">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E24" s="15">
-        <v>-45.454545454545</v>
+        <v>26.666666666666</v>
       </c>
       <c r="F24" s="14">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="G24" s="14">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H24" s="15">
-        <v>-14.634146341463</v>
+        <v>-1.298701298701</v>
       </c>
       <c r="I24" s="14">
-        <v>220</v>
+        <v>238</v>
       </c>
       <c r="J24" s="14">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="K24" s="15">
-        <v>-0.900900900900</v>
+        <v>0.421940928270</v>
       </c>
       <c r="L24" s="15">
-        <v>-16.666666666666</v>
+        <v>-17.361111111111</v>
       </c>
       <c r="M24" s="15">
-        <v>42.857142857142</v>
+        <v>39.181286549707</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D25" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E25" s="15">
-        <v>-50</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="F25" s="14">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G25" s="14">
         <v>25</v>
       </c>
       <c r="H25" s="15">
-        <v>-28</v>
+        <v>-16</v>
       </c>
       <c r="I25" s="14">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="J25" s="14">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="K25" s="15">
-        <v>-46.835443037974</v>
+        <v>-46.590909090909</v>
       </c>
       <c r="L25" s="15">
-        <v>-63.793103448275</v>
+        <v>-64.661654135338</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D26" s="14">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E26" s="15">
-        <v>-42.857142857142</v>
+        <v>42.857142857142</v>
       </c>
       <c r="F26" s="14">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G26" s="14">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H26" s="15">
-        <v>35.135135135135</v>
+        <v>38.461538461538</v>
       </c>
       <c r="I26" s="14">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="J26" s="14">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="K26" s="15">
-        <v>-20.930232558139</v>
+        <v>-16.911764705882</v>
       </c>
       <c r="L26" s="15">
-        <v>6.25</v>
+        <v>14.141414141414</v>
       </c>
       <c r="M26" s="15">
-        <v>14.606741573033</v>
+        <v>21.505376344086</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="C27" s="14">
+        <v>3</v>
+      </c>
+      <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
+        <v>200</v>
       </c>
       <c r="F27" s="14">
-        <v>6</v>
-      </c>
-      <c r="G27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H27" s="13" t="s">
-        <v>21</v>
+        <v>8</v>
+      </c>
+      <c r="G27" s="14">
+        <v>1</v>
+      </c>
+      <c r="H27" s="15">
+        <v>700</v>
       </c>
       <c r="I27" s="14">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J27" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K27" s="15">
-        <v>266.666666666667</v>
+        <v>250</v>
       </c>
       <c r="L27" s="15">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>4</v>
-      </c>
-      <c r="D28" s="14">
         <v>1</v>
       </c>
-      <c r="E28" s="15">
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28" s="14">
+        <v>12</v>
+      </c>
+      <c r="G28" s="14">
+        <v>3</v>
+      </c>
+      <c r="H28" s="15">
         <v>300</v>
       </c>
-      <c r="F28" s="14">
-        <v>11</v>
-      </c>
-      <c r="G28" s="14">
-        <v>6</v>
-      </c>
-      <c r="H28" s="15">
-        <v>83.333333333333</v>
-      </c>
       <c r="I28" s="14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J28" s="14">
         <v>13</v>
       </c>
       <c r="K28" s="15">
-        <v>61.538461538461</v>
+        <v>69.230769230769</v>
       </c>
       <c r="L28" s="15">
-        <v>162.5</v>
+        <v>144.444444444444</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1558,7 +1558,7 @@
         <v>21</v>
       </c>
       <c r="F31" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-107pct.xlsx
+++ b/data/source/weekly/cs-en-us-107pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">14</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/23/2026</t>
+      <t xml:space="preserve">3/30/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/29/2026</t>
+      <t xml:space="preserve">4/5/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
@@ -879,7 +879,7 @@
         <v>-66.666666666666</v>
       </c>
       <c r="L14" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="M14" s="15">
         <v>0</v>
@@ -892,23 +892,23 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>2</v>
-      </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>100</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G15" s="14">
         <v>1</v>
       </c>
       <c r="H15" s="15">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="I15" s="14">
         <v>10</v>
@@ -926,7 +926,7 @@
         <v>400</v>
       </c>
       <c r="N15" s="15">
-        <v>11.111111111111</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D16" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F16" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G16" s="14">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H16" s="15">
-        <v>-18.181818181818</v>
+        <v>-12.5</v>
       </c>
       <c r="I16" s="14">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J16" s="14">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K16" s="15">
-        <v>-6.666666666666</v>
+        <v>-6.451612903225</v>
       </c>
       <c r="L16" s="15">
-        <v>0</v>
+        <v>-3.333333333333</v>
       </c>
       <c r="M16" s="15">
-        <v>-58.208955223880</v>
+        <v>-58.571428571428</v>
       </c>
       <c r="N16" s="15">
-        <v>-88.333333333333</v>
+        <v>-88.627450980392</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
+        <v>6</v>
+      </c>
+      <c r="D17" s="14">
         <v>3</v>
       </c>
-      <c r="D17" s="14">
-        <v>5</v>
-      </c>
       <c r="E17" s="15">
-        <v>-40</v>
+        <v>100</v>
       </c>
       <c r="F17" s="14">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G17" s="14">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="H17" s="15">
-        <v>-34.782608695652</v>
+        <v>0</v>
       </c>
       <c r="I17" s="14">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J17" s="14">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="K17" s="15">
+        <v>-27.272727272727</v>
+      </c>
+      <c r="L17" s="15">
         <v>-33.333333333333</v>
       </c>
-      <c r="L17" s="15">
-        <v>-39.130434782608</v>
-      </c>
       <c r="M17" s="15">
-        <v>110</v>
+        <v>128.571428571429</v>
       </c>
       <c r="N17" s="15">
-        <v>-27.586206896551</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D18" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E18" s="15">
-        <v>-42.857142857142</v>
+        <v>-90</v>
       </c>
       <c r="F18" s="14">
         <v>11</v>
       </c>
       <c r="G18" s="14">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="H18" s="15">
-        <v>-47.619047619047</v>
+        <v>-62.068965517241</v>
       </c>
       <c r="I18" s="14">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="J18" s="14">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="K18" s="15">
-        <v>-46.031746031746</v>
+        <v>-49.315068493150</v>
       </c>
       <c r="L18" s="15">
-        <v>-38.181818181818</v>
+        <v>-40.322580645161</v>
       </c>
       <c r="M18" s="15">
-        <v>-43.333333333333</v>
+        <v>-44.776119402985</v>
       </c>
       <c r="N18" s="15">
-        <v>-91.168831168831</v>
+        <v>-90.818858560794</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D19" s="14">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E19" s="15">
-        <v>33.333333333333</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F19" s="14">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G19" s="14">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="H19" s="15">
-        <v>32.5</v>
+        <v>4.255319148936</v>
       </c>
       <c r="I19" s="14">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="J19" s="14">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="K19" s="15">
-        <v>20.720720720720</v>
+        <v>14.285714285714</v>
       </c>
       <c r="L19" s="15">
-        <v>-7.586206896551</v>
+        <v>-10</v>
       </c>
       <c r="M19" s="15">
-        <v>15.517241379310</v>
+        <v>16.129032258064</v>
       </c>
       <c r="N19" s="15">
-        <v>7.2</v>
+        <v>5.109489051094</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D20" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E20" s="15">
-        <v>-37.5</v>
+        <v>100</v>
       </c>
       <c r="F20" s="14">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G20" s="14">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H20" s="15">
-        <v>26.923076923076</v>
+        <v>25</v>
       </c>
       <c r="I20" s="14">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="J20" s="14">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="K20" s="15">
-        <v>-12.941176470588</v>
+        <v>-5.494505494505</v>
       </c>
       <c r="L20" s="15">
-        <v>1.369863013698</v>
+        <v>14.666666666666</v>
       </c>
       <c r="M20" s="15">
-        <v>60.869565217391</v>
+        <v>72</v>
       </c>
       <c r="N20" s="15">
-        <v>-93.626184323858</v>
+        <v>-93.158313444709</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D21" s="17">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E21" s="18">
-        <v>-9.375</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="F21" s="17">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G21" s="17">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="H21" s="18">
-        <v>4.918032786885</v>
+        <v>-4.545454545454</v>
       </c>
       <c r="I21" s="17">
-        <v>323</v>
+        <v>355</v>
       </c>
       <c r="J21" s="17">
-        <v>358</v>
+        <v>393</v>
       </c>
       <c r="K21" s="18">
-        <v>-9.776536312849</v>
+        <v>-9.669211195928</v>
       </c>
       <c r="L21" s="18">
-        <v>-14.550264550264</v>
+        <v>-12.990196078431</v>
       </c>
       <c r="M21" s="18">
-        <v>3.525641025641</v>
+        <v>5.970149253731</v>
       </c>
       <c r="N21" s="18">
-        <v>-83.686868686868</v>
+        <v>-83.286252354049</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,7 +1180,7 @@
         <v>29</v>
       </c>
       <c r="C22" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1189,28 +1189,28 @@
         <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>2</v>
-      </c>
-      <c r="G22" s="14">
-        <v>2</v>
-      </c>
-      <c r="H22" s="15">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="G22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I22" s="14">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J22" s="14">
         <v>5</v>
       </c>
       <c r="K22" s="15">
-        <v>160</v>
+        <v>220</v>
       </c>
       <c r="L22" s="15">
-        <v>0</v>
+        <v>23.076923076923</v>
       </c>
       <c r="M22" s="15">
-        <v>116.666666666667</v>
+        <v>166.666666666667</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1230,10 +1230,10 @@
         <v>21</v>
       </c>
       <c r="F23" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G23" s="14">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H23" s="15">
         <v>-80</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D24" s="14">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="E24" s="15">
-        <v>26.666666666666</v>
+        <v>-25</v>
       </c>
       <c r="F24" s="14">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G24" s="14">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="H24" s="15">
-        <v>-1.298701298701</v>
+        <v>-12.048192771084</v>
       </c>
       <c r="I24" s="14">
-        <v>238</v>
+        <v>255</v>
       </c>
       <c r="J24" s="14">
-        <v>237</v>
+        <v>261</v>
       </c>
       <c r="K24" s="15">
-        <v>0.421940928270</v>
+        <v>-2.298850574712</v>
       </c>
       <c r="L24" s="15">
-        <v>-17.361111111111</v>
+        <v>-18.789808917197</v>
       </c>
       <c r="M24" s="15">
-        <v>39.181286549707</v>
+        <v>32.8125</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1302,35 +1302,35 @@
       <c r="A25" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="14">
-        <v>5</v>
+      <c r="C25" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D25" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E25" s="15">
-        <v>-44.444444444444</v>
+        <v>-100</v>
       </c>
       <c r="F25" s="14">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G25" s="14">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="H25" s="15">
-        <v>-16</v>
+        <v>-51.612903225806</v>
       </c>
       <c r="I25" s="14">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J25" s="14">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="K25" s="15">
-        <v>-46.590909090909</v>
+        <v>-52.083333333333</v>
       </c>
       <c r="L25" s="15">
-        <v>-64.661654135338</v>
+        <v>-69.333333333333</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D26" s="14">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E26" s="15">
-        <v>42.857142857142</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="F26" s="14">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="G26" s="14">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H26" s="15">
-        <v>38.461538461538</v>
+        <v>15.789473684210</v>
       </c>
       <c r="I26" s="14">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="J26" s="14">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="K26" s="15">
-        <v>-16.911764705882</v>
+        <v>-16.216216216216</v>
       </c>
       <c r="L26" s="15">
-        <v>14.141414141414</v>
+        <v>14.814814814814</v>
       </c>
       <c r="M26" s="15">
-        <v>21.505376344086</v>
+        <v>25.252525252525</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>3</v>
-      </c>
-      <c r="D27" s="14">
-        <v>1</v>
-      </c>
-      <c r="E27" s="15">
-        <v>200</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G27" s="14">
         <v>1</v>
       </c>
       <c r="H27" s="15">
-        <v>700</v>
+        <v>400</v>
       </c>
       <c r="I27" s="14">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J27" s="14">
         <v>4</v>
       </c>
       <c r="K27" s="15">
-        <v>250</v>
+        <v>225</v>
       </c>
       <c r="L27" s="15">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,32 +1428,32 @@
       <c r="C28" s="14">
         <v>1</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="D28" s="14">
+        <v>2</v>
+      </c>
+      <c r="E28" s="15">
+        <v>-50</v>
       </c>
       <c r="F28" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G28" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H28" s="15">
-        <v>300</v>
+        <v>160</v>
       </c>
       <c r="I28" s="14">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J28" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K28" s="15">
-        <v>69.230769230769</v>
+        <v>60</v>
       </c>
       <c r="L28" s="15">
-        <v>144.444444444444</v>
+        <v>118.181818181818</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1558,7 +1558,7 @@
         <v>21</v>
       </c>
       <c r="F31" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
@@ -1567,16 +1567,16 @@
         <v>21</v>
       </c>
       <c r="I31" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J31" s="14">
         <v>3</v>
       </c>
       <c r="K31" s="15">
-        <v>33.333333333333</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L31" s="15">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-107pct.xlsx
+++ b/data/source/weekly/cs-en-us-107pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">15</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/30/2026</t>
+      <t xml:space="preserve">4/6/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/5/2026</t>
+      <t xml:space="preserve">4/12/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
@@ -860,8 +860,8 @@
       <c r="E14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="14">
-        <v>1</v>
+      <c r="F14" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>20</v>
@@ -892,8 +892,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="14">
+        <v>3</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -902,31 +902,31 @@
         <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G15" s="14">
         <v>1</v>
       </c>
       <c r="H15" s="15">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="I15" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J15" s="14">
         <v>3</v>
       </c>
       <c r="K15" s="15">
-        <v>233.333333333333</v>
+        <v>333.333333333333</v>
       </c>
       <c r="L15" s="15">
-        <v>42.857142857142</v>
+        <v>62.5</v>
       </c>
       <c r="M15" s="15">
-        <v>400</v>
+        <v>550</v>
       </c>
       <c r="N15" s="15">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,13 +934,13 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" s="14">
         <v>1</v>
       </c>
       <c r="E16" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F16" s="14">
         <v>7</v>
@@ -952,22 +952,22 @@
         <v>-12.5</v>
       </c>
       <c r="I16" s="14">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J16" s="14">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K16" s="15">
-        <v>-6.451612903225</v>
+        <v>-3.125</v>
       </c>
       <c r="L16" s="15">
-        <v>-3.333333333333</v>
+        <v>-6.060606060606</v>
       </c>
       <c r="M16" s="15">
-        <v>-58.571428571428</v>
+        <v>-58.666666666666</v>
       </c>
       <c r="N16" s="15">
-        <v>-88.627450980392</v>
+        <v>-88.345864661654</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
+        <v>11</v>
+      </c>
+      <c r="D17" s="14">
         <v>6</v>
       </c>
-      <c r="D17" s="14">
-        <v>3</v>
-      </c>
       <c r="E17" s="15">
-        <v>100</v>
+        <v>83.333333333333</v>
       </c>
       <c r="F17" s="14">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G17" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H17" s="15">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I17" s="14">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="J17" s="14">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K17" s="15">
-        <v>-27.272727272727</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="L17" s="15">
-        <v>-33.333333333333</v>
+        <v>-18.918918918918</v>
       </c>
       <c r="M17" s="15">
-        <v>128.571428571429</v>
+        <v>160.869565217391</v>
       </c>
       <c r="N17" s="15">
-        <v>-20</v>
+        <v>-3.225806451612</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D18" s="14">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E18" s="15">
-        <v>-90</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F18" s="14">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G18" s="14">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H18" s="15">
-        <v>-62.068965517241</v>
+        <v>-42.307692307692</v>
       </c>
       <c r="I18" s="14">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="J18" s="14">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="K18" s="15">
-        <v>-49.315068493150</v>
+        <v>-43.421052631578</v>
       </c>
       <c r="L18" s="15">
-        <v>-40.322580645161</v>
+        <v>-32.8125</v>
       </c>
       <c r="M18" s="15">
-        <v>-44.776119402985</v>
+        <v>-39.436619718309</v>
       </c>
       <c r="N18" s="15">
-        <v>-90.818858560794</v>
+        <v>-90.092165898617</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
+        <v>19</v>
+      </c>
+      <c r="D19" s="14">
         <v>10</v>
       </c>
-      <c r="D19" s="14">
-        <v>15</v>
-      </c>
       <c r="E19" s="15">
-        <v>-33.333333333333</v>
+        <v>90</v>
       </c>
       <c r="F19" s="14">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="G19" s="14">
         <v>47</v>
       </c>
       <c r="H19" s="15">
-        <v>4.255319148936</v>
+        <v>14.893617021276</v>
       </c>
       <c r="I19" s="14">
-        <v>144</v>
+        <v>162</v>
       </c>
       <c r="J19" s="14">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="K19" s="15">
-        <v>14.285714285714</v>
+        <v>19.117647058823</v>
       </c>
       <c r="L19" s="15">
-        <v>-10</v>
+        <v>-6.358381502890</v>
       </c>
       <c r="M19" s="15">
-        <v>16.129032258064</v>
+        <v>24.615384615384</v>
       </c>
       <c r="N19" s="15">
-        <v>5.109489051094</v>
+        <v>5.882352941176</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D20" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E20" s="15">
-        <v>100</v>
+        <v>-75</v>
       </c>
       <c r="F20" s="14">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G20" s="14">
         <v>28</v>
       </c>
       <c r="H20" s="15">
-        <v>25</v>
+        <v>14.285714285714</v>
       </c>
       <c r="I20" s="14">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="J20" s="14">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="K20" s="15">
-        <v>-5.494505494505</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="L20" s="15">
-        <v>14.666666666666</v>
+        <v>11.392405063291</v>
       </c>
       <c r="M20" s="15">
-        <v>72</v>
+        <v>62.962962962963</v>
       </c>
       <c r="N20" s="15">
-        <v>-93.158313444709</v>
+        <v>-93.476649369903</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="D21" s="17">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E21" s="18">
-        <v>-14.285714285714</v>
+        <v>50</v>
       </c>
       <c r="F21" s="17">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="G21" s="17">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="H21" s="18">
-        <v>-4.545454545454</v>
+        <v>5.384615384615</v>
       </c>
       <c r="I21" s="17">
-        <v>355</v>
+        <v>398</v>
       </c>
       <c r="J21" s="17">
-        <v>393</v>
+        <v>421</v>
       </c>
       <c r="K21" s="18">
-        <v>-9.669211195928</v>
+        <v>-5.463182897862</v>
       </c>
       <c r="L21" s="18">
-        <v>-12.990196078431</v>
+        <v>-8.083140877598</v>
       </c>
       <c r="M21" s="18">
-        <v>5.970149253731</v>
+        <v>11.797752808988</v>
       </c>
       <c r="N21" s="18">
-        <v>-83.286252354049</v>
+        <v>-82.513181019332</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,17 +1180,17 @@
         <v>29</v>
       </c>
       <c r="C22" s="14">
+        <v>1</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="14">
         <v>3</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F22" s="14">
-        <v>4</v>
-      </c>
       <c r="G22" s="13" t="s">
         <v>20</v>
       </c>
@@ -1198,19 +1198,19 @@
         <v>21</v>
       </c>
       <c r="I22" s="14">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J22" s="14">
         <v>5</v>
       </c>
       <c r="K22" s="15">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="L22" s="15">
-        <v>23.076923076923</v>
+        <v>15.384615384615</v>
       </c>
       <c r="M22" s="15">
-        <v>166.666666666667</v>
+        <v>87.5</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,8 +1220,8 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
+      <c r="C23" s="14">
+        <v>4</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>20</v>
@@ -1230,28 +1230,28 @@
         <v>21</v>
       </c>
       <c r="F23" s="14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G23" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H23" s="15">
-        <v>-80</v>
+        <v>25</v>
       </c>
       <c r="I23" s="14">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J23" s="14">
         <v>19</v>
       </c>
       <c r="K23" s="15">
-        <v>-57.894736842105</v>
+        <v>-31.578947368421</v>
       </c>
       <c r="L23" s="15">
-        <v>-33.333333333333</v>
+        <v>8.333333333333</v>
       </c>
       <c r="M23" s="15">
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
+        <v>11</v>
+      </c>
+      <c r="D24" s="14">
         <v>18</v>
       </c>
-      <c r="D24" s="14">
-        <v>24</v>
-      </c>
       <c r="E24" s="15">
-        <v>-25</v>
+        <v>-38.888888888888</v>
       </c>
       <c r="F24" s="14">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="G24" s="14">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="H24" s="15">
-        <v>-12.048192771084</v>
+        <v>-25.316455696202</v>
       </c>
       <c r="I24" s="14">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="J24" s="14">
-        <v>261</v>
+        <v>279</v>
       </c>
       <c r="K24" s="15">
-        <v>-2.298850574712</v>
+        <v>-4.659498207885</v>
       </c>
       <c r="L24" s="15">
-        <v>-18.789808917197</v>
+        <v>-19.879518072289</v>
       </c>
       <c r="M24" s="15">
-        <v>32.8125</v>
+        <v>23.720930232558</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1302,35 +1302,35 @@
       <c r="A25" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="13" t="s">
-        <v>20</v>
+      <c r="C25" s="14">
+        <v>4</v>
       </c>
       <c r="D25" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E25" s="15">
-        <v>-100</v>
+        <v>-20</v>
       </c>
       <c r="F25" s="14">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G25" s="14">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H25" s="15">
-        <v>-51.612903225806</v>
+        <v>-60</v>
       </c>
       <c r="I25" s="14">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="J25" s="14">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="K25" s="15">
-        <v>-52.083333333333</v>
+        <v>-50.495049504950</v>
       </c>
       <c r="L25" s="15">
-        <v>-69.333333333333</v>
+        <v>-68.152866242038</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D26" s="14">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E26" s="15">
-        <v>-8.333333333333</v>
+        <v>100</v>
       </c>
       <c r="F26" s="14">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G26" s="14">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H26" s="15">
-        <v>15.789473684210</v>
+        <v>7.692307692307</v>
       </c>
       <c r="I26" s="14">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="J26" s="14">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="K26" s="15">
-        <v>-16.216216216216</v>
+        <v>-12.337662337662</v>
       </c>
       <c r="L26" s="15">
-        <v>14.814814814814</v>
+        <v>12.5</v>
       </c>
       <c r="M26" s="15">
-        <v>25.252525252525</v>
+        <v>20.535714285714</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>3</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1403,16 +1403,16 @@
         <v>400</v>
       </c>
       <c r="I27" s="14">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J27" s="14">
         <v>4</v>
       </c>
       <c r="K27" s="15">
-        <v>225</v>
+        <v>300</v>
       </c>
       <c r="L27" s="15">
-        <v>30</v>
+        <v>45.454545454545</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
+        <v>3</v>
+      </c>
+      <c r="D28" s="14">
         <v>1</v>
       </c>
-      <c r="D28" s="14">
-        <v>2</v>
-      </c>
       <c r="E28" s="15">
-        <v>-50</v>
+        <v>200</v>
       </c>
       <c r="F28" s="14">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G28" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H28" s="15">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="I28" s="14">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J28" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K28" s="15">
-        <v>60</v>
+        <v>68.75</v>
       </c>
       <c r="L28" s="15">
-        <v>118.181818181818</v>
+        <v>145.454545454545</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1558,7 +1558,7 @@
         <v>21</v>
       </c>
       <c r="F31" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-107pct.xlsx
+++ b/data/source/weekly/cs-en-us-107pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">15</t>
+      <t xml:space="preserve">16</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/6/2026</t>
+      <t xml:space="preserve">4/13/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/12/2026</t>
+      <t xml:space="preserve">4/19/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
@@ -895,38 +895,38 @@
       <c r="C15" s="14">
         <v>3</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>200</v>
       </c>
       <c r="F15" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H15" s="15">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="I15" s="14">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J15" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K15" s="15">
-        <v>333.333333333333</v>
+        <v>300</v>
       </c>
       <c r="L15" s="15">
-        <v>62.5</v>
+        <v>77.777777777777</v>
       </c>
       <c r="M15" s="15">
-        <v>550</v>
+        <v>700</v>
       </c>
       <c r="N15" s="15">
-        <v>30</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D16" s="14">
         <v>1</v>
       </c>
       <c r="E16" s="15">
+        <v>300</v>
+      </c>
+      <c r="F16" s="14">
+        <v>10</v>
+      </c>
+      <c r="G16" s="14">
+        <v>5</v>
+      </c>
+      <c r="H16" s="15">
         <v>100</v>
       </c>
-      <c r="F16" s="14">
-        <v>7</v>
-      </c>
-      <c r="G16" s="14">
-        <v>8</v>
-      </c>
-      <c r="H16" s="15">
-        <v>-12.5</v>
-      </c>
       <c r="I16" s="14">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J16" s="14">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K16" s="15">
-        <v>-3.125</v>
+        <v>6.060606060606</v>
       </c>
       <c r="L16" s="15">
-        <v>-6.060606060606</v>
+        <v>-10.256410256410</v>
       </c>
       <c r="M16" s="15">
-        <v>-58.666666666666</v>
+        <v>-56.25</v>
       </c>
       <c r="N16" s="15">
-        <v>-88.345864661654</v>
+        <v>-87.455197132616</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D17" s="14">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E17" s="15">
-        <v>83.333333333333</v>
+        <v>500</v>
       </c>
       <c r="F17" s="14">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G17" s="14">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H17" s="15">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="I17" s="14">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="J17" s="14">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K17" s="15">
-        <v>-16.666666666666</v>
+        <v>-6.849315068493</v>
       </c>
       <c r="L17" s="15">
-        <v>-18.918918918918</v>
+        <v>-15</v>
       </c>
       <c r="M17" s="15">
-        <v>160.869565217391</v>
+        <v>161.538461538462</v>
       </c>
       <c r="N17" s="15">
-        <v>-3.225806451612</v>
+        <v>4.615384615384</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D18" s="14">
         <v>3</v>
       </c>
       <c r="E18" s="15">
-        <v>66.666666666666</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F18" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G18" s="14">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="H18" s="15">
-        <v>-42.307692307692</v>
+        <v>-26.086956521739</v>
       </c>
       <c r="I18" s="14">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="J18" s="14">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="K18" s="15">
-        <v>-43.421052631578</v>
+        <v>-40.506329113924</v>
       </c>
       <c r="L18" s="15">
-        <v>-32.8125</v>
+        <v>-28.787878787878</v>
       </c>
       <c r="M18" s="15">
-        <v>-39.436619718309</v>
+        <v>-37.333333333333</v>
       </c>
       <c r="N18" s="15">
-        <v>-90.092165898617</v>
+        <v>-89.715536105032</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D19" s="14">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E19" s="15">
-        <v>90</v>
+        <v>71.428571428571</v>
       </c>
       <c r="F19" s="14">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="G19" s="14">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H19" s="15">
-        <v>14.893617021276</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I19" s="14">
-        <v>162</v>
+        <v>187</v>
       </c>
       <c r="J19" s="14">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="K19" s="15">
-        <v>19.117647058823</v>
+        <v>24.666666666666</v>
       </c>
       <c r="L19" s="15">
-        <v>-6.358381502890</v>
+        <v>2.747252747252</v>
       </c>
       <c r="M19" s="15">
-        <v>24.615384615384</v>
+        <v>30.769230769230</v>
       </c>
       <c r="N19" s="15">
-        <v>5.882352941176</v>
+        <v>12.650602409638</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D20" s="14">
         <v>8</v>
       </c>
       <c r="E20" s="15">
-        <v>-75</v>
+        <v>-50</v>
       </c>
       <c r="F20" s="14">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="G20" s="14">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H20" s="15">
-        <v>14.285714285714</v>
+        <v>-23.333333333333</v>
       </c>
       <c r="I20" s="14">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="J20" s="14">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="K20" s="15">
-        <v>-11.111111111111</v>
+        <v>-14.018691588785</v>
       </c>
       <c r="L20" s="15">
-        <v>11.392405063291</v>
+        <v>5.747126436781</v>
       </c>
       <c r="M20" s="15">
-        <v>62.962962962963</v>
+        <v>61.403508771929</v>
       </c>
       <c r="N20" s="15">
-        <v>-93.476649369903</v>
+        <v>-93.570929419986</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D21" s="17">
         <v>28</v>
       </c>
       <c r="E21" s="18">
-        <v>50</v>
+        <v>60.714285714285</v>
       </c>
       <c r="F21" s="17">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="G21" s="17">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="H21" s="18">
-        <v>5.384615384615</v>
+        <v>21.138211382113</v>
       </c>
       <c r="I21" s="17">
-        <v>398</v>
+        <v>446</v>
       </c>
       <c r="J21" s="17">
-        <v>421</v>
+        <v>449</v>
       </c>
       <c r="K21" s="18">
-        <v>-5.463182897862</v>
+        <v>-0.668151447661</v>
       </c>
       <c r="L21" s="18">
-        <v>-8.083140877598</v>
+        <v>-4.086021505376</v>
       </c>
       <c r="M21" s="18">
-        <v>11.797752808988</v>
+        <v>16.145833333333</v>
       </c>
       <c r="N21" s="18">
-        <v>-82.513181019332</v>
+        <v>-81.49377593361</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,7 +1180,7 @@
         <v>29</v>
       </c>
       <c r="C22" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1189,7 +1189,7 @@
         <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>20</v>
@@ -1198,19 +1198,19 @@
         <v>21</v>
       </c>
       <c r="I22" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J22" s="14">
         <v>5</v>
       </c>
       <c r="K22" s="15">
-        <v>200</v>
+        <v>240</v>
       </c>
       <c r="L22" s="15">
-        <v>15.384615384615</v>
+        <v>13.333333333333</v>
       </c>
       <c r="M22" s="15">
-        <v>87.5</v>
+        <v>112.5</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,7 +1221,7 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>20</v>
@@ -1232,26 +1232,26 @@
       <c r="F23" s="14">
         <v>5</v>
       </c>
-      <c r="G23" s="14">
-        <v>4</v>
-      </c>
-      <c r="H23" s="15">
-        <v>25</v>
+      <c r="G23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I23" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J23" s="14">
         <v>19</v>
       </c>
       <c r="K23" s="15">
-        <v>-31.578947368421</v>
+        <v>-26.315789473684</v>
       </c>
       <c r="L23" s="15">
-        <v>8.333333333333</v>
+        <v>16.666666666666</v>
       </c>
       <c r="M23" s="15">
-        <v>62.5</v>
+        <v>75</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D24" s="14">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="E24" s="15">
-        <v>-38.888888888888</v>
+        <v>-48.484848484848</v>
       </c>
       <c r="F24" s="14">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G24" s="14">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H24" s="15">
-        <v>-25.316455696202</v>
+        <v>-28.888888888888</v>
       </c>
       <c r="I24" s="14">
-        <v>266</v>
+        <v>283</v>
       </c>
       <c r="J24" s="14">
-        <v>279</v>
+        <v>312</v>
       </c>
       <c r="K24" s="15">
-        <v>-4.659498207885</v>
+        <v>-9.294871794871</v>
       </c>
       <c r="L24" s="15">
-        <v>-19.879518072289</v>
+        <v>-20.281690140845</v>
       </c>
       <c r="M24" s="15">
-        <v>23.720930232558</v>
+        <v>17.427385892116</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D25" s="14">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E25" s="15">
-        <v>-20</v>
+        <v>-61.538461538461</v>
       </c>
       <c r="F25" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G25" s="14">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H25" s="15">
-        <v>-60</v>
+        <v>-62.857142857142</v>
       </c>
       <c r="I25" s="14">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="J25" s="14">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="K25" s="15">
-        <v>-50.495049504950</v>
+        <v>-51.754385964912</v>
       </c>
       <c r="L25" s="15">
-        <v>-68.152866242038</v>
+        <v>-66.257668711656</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D26" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E26" s="15">
-        <v>100</v>
+        <v>62.5</v>
       </c>
       <c r="F26" s="14">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G26" s="14">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="H26" s="15">
-        <v>7.692307692307</v>
+        <v>36.363636363636</v>
       </c>
       <c r="I26" s="14">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="J26" s="14">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="K26" s="15">
-        <v>-12.337662337662</v>
+        <v>-9.259259259259</v>
       </c>
       <c r="L26" s="15">
-        <v>12.5</v>
+        <v>8.088235294117</v>
       </c>
       <c r="M26" s="15">
-        <v>20.535714285714</v>
+        <v>26.724137931034</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,32 +1387,32 @@
       <c r="C27" s="14">
         <v>3</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
+        <v>200</v>
       </c>
       <c r="F27" s="14">
+        <v>8</v>
+      </c>
+      <c r="G27" s="14">
+        <v>2</v>
+      </c>
+      <c r="H27" s="15">
+        <v>300</v>
+      </c>
+      <c r="I27" s="14">
+        <v>19</v>
+      </c>
+      <c r="J27" s="14">
         <v>5</v>
       </c>
-      <c r="G27" s="14">
-        <v>1</v>
-      </c>
-      <c r="H27" s="15">
-        <v>400</v>
-      </c>
-      <c r="I27" s="14">
-        <v>16</v>
-      </c>
-      <c r="J27" s="14">
-        <v>4</v>
-      </c>
       <c r="K27" s="15">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="L27" s="15">
-        <v>45.454545454545</v>
+        <v>46.153846153846</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>3</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D28" s="14">
         <v>1</v>
       </c>
       <c r="E28" s="15">
-        <v>200</v>
+        <v>-100</v>
       </c>
       <c r="F28" s="14">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G28" s="14">
         <v>4</v>
       </c>
       <c r="H28" s="15">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="I28" s="14">
         <v>27</v>
       </c>
       <c r="J28" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K28" s="15">
-        <v>68.75</v>
+        <v>58.823529411764</v>
       </c>
       <c r="L28" s="15">
-        <v>145.454545454545</v>
+        <v>125</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1548,8 +1548,8 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
+      <c r="C31" s="14">
+        <v>1</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>
@@ -1558,7 +1558,7 @@
         <v>21</v>
       </c>
       <c r="F31" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
@@ -1567,16 +1567,16 @@
         <v>21</v>
       </c>
       <c r="I31" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J31" s="14">
         <v>3</v>
       </c>
       <c r="K31" s="15">
-        <v>66.666666666666</v>
+        <v>133.333333333333</v>
       </c>
       <c r="L31" s="15">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1607,8 +1607,8 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="13" t="s">
-        <v>20</v>
+      <c r="C33" s="14">
+        <v>1</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>
@@ -1616,8 +1616,8 @@
       <c r="E33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F33" s="13" t="s">
-        <v>20</v>
+      <c r="F33" s="14">
+        <v>1</v>
       </c>
       <c r="G33" s="13" t="s">
         <v>20</v>
@@ -1625,8 +1625,8 @@
       <c r="H33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I33" s="13" t="s">
-        <v>20</v>
+      <c r="I33" s="14">
+        <v>1</v>
       </c>
       <c r="J33" s="13" t="s">
         <v>20</v>
@@ -1635,7 +1635,7 @@
         <v>21</v>
       </c>
       <c r="L33" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-107pct.xlsx
+++ b/data/source/weekly/cs-en-us-107pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">16</t>
+      <t xml:space="preserve">17</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/13/2026</t>
+      <t xml:space="preserve">4/20/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/19/2026</t>
+      <t xml:space="preserve">4/26/2026</t>
     </r>
   </si>
   <si>
@@ -893,22 +893,22 @@
         <v>22</v>
       </c>
       <c r="C15" s="14">
-        <v>3</v>
-      </c>
-      <c r="D15" s="14">
         <v>1</v>
       </c>
-      <c r="E15" s="15">
-        <v>200</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G15" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H15" s="15">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="I15" s="14">
         <v>16</v>
@@ -926,48 +926,48 @@
         <v>700</v>
       </c>
       <c r="N15" s="15">
-        <v>60</v>
+        <v>33.333333333333</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="14">
-        <v>4</v>
+      <c r="C16" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D16" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" s="15">
-        <v>300</v>
+        <v>-100</v>
       </c>
       <c r="F16" s="14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G16" s="14">
         <v>5</v>
       </c>
       <c r="H16" s="15">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="I16" s="14">
         <v>35</v>
       </c>
       <c r="J16" s="14">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K16" s="15">
-        <v>6.060606060606</v>
+        <v>0</v>
       </c>
       <c r="L16" s="15">
-        <v>-10.256410256410</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="M16" s="15">
-        <v>-56.25</v>
+        <v>-60.227272727272</v>
       </c>
       <c r="N16" s="15">
-        <v>-87.455197132616</v>
+        <v>-88.135593220339</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,13 +975,13 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D17" s="14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E17" s="15">
-        <v>500</v>
+        <v>-20</v>
       </c>
       <c r="F17" s="14">
         <v>27</v>
@@ -993,22 +993,22 @@
         <v>80</v>
       </c>
       <c r="I17" s="14">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="J17" s="14">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="K17" s="15">
-        <v>-6.849315068493</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="L17" s="15">
-        <v>-15</v>
+        <v>-21.739130434782</v>
       </c>
       <c r="M17" s="15">
-        <v>161.538461538462</v>
+        <v>157.142857142857</v>
       </c>
       <c r="N17" s="15">
-        <v>4.615384615384</v>
+        <v>4.347826086956</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
+        <v>5</v>
+      </c>
+      <c r="D18" s="14">
         <v>4</v>
       </c>
-      <c r="D18" s="14">
-        <v>3</v>
-      </c>
       <c r="E18" s="15">
-        <v>33.333333333333</v>
+        <v>25</v>
       </c>
       <c r="F18" s="14">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G18" s="14">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H18" s="15">
-        <v>-26.086956521739</v>
+        <v>-20</v>
       </c>
       <c r="I18" s="14">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="J18" s="14">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="K18" s="15">
-        <v>-40.506329113924</v>
+        <v>-37.349397590361</v>
       </c>
       <c r="L18" s="15">
-        <v>-28.787878787878</v>
+        <v>-32.467532467532</v>
       </c>
       <c r="M18" s="15">
-        <v>-37.333333333333</v>
+        <v>-31.578947368421</v>
       </c>
       <c r="N18" s="15">
-        <v>-89.715536105032</v>
+        <v>-89.278350515463</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D19" s="14">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E19" s="15">
-        <v>71.428571428571</v>
+        <v>110</v>
       </c>
       <c r="F19" s="14">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="G19" s="14">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H19" s="15">
-        <v>33.333333333333</v>
+        <v>48.979591836734</v>
       </c>
       <c r="I19" s="14">
-        <v>187</v>
+        <v>208</v>
       </c>
       <c r="J19" s="14">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="K19" s="15">
-        <v>24.666666666666</v>
+        <v>30</v>
       </c>
       <c r="L19" s="15">
-        <v>2.747252747252</v>
+        <v>8.900523560209</v>
       </c>
       <c r="M19" s="15">
-        <v>30.769230769230</v>
+        <v>38.666666666666</v>
       </c>
       <c r="N19" s="15">
-        <v>12.650602409638</v>
+        <v>12.432432432432</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1107,31 +1107,31 @@
         <v>-50</v>
       </c>
       <c r="F20" s="14">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G20" s="14">
         <v>30</v>
       </c>
       <c r="H20" s="15">
-        <v>-23.333333333333</v>
+        <v>-30</v>
       </c>
       <c r="I20" s="14">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="J20" s="14">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="K20" s="15">
-        <v>-14.018691588785</v>
+        <v>-17.391304347826</v>
       </c>
       <c r="L20" s="15">
-        <v>5.747126436781</v>
+        <v>-2.061855670103</v>
       </c>
       <c r="M20" s="15">
-        <v>61.403508771929</v>
+        <v>53.225806451612</v>
       </c>
       <c r="N20" s="15">
-        <v>-93.570929419986</v>
+        <v>-93.839169909208</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="D21" s="17">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E21" s="18">
-        <v>60.714285714285</v>
+        <v>20.689655172413</v>
       </c>
       <c r="F21" s="17">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G21" s="17">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H21" s="18">
-        <v>21.138211382113</v>
+        <v>25</v>
       </c>
       <c r="I21" s="17">
-        <v>446</v>
+        <v>479</v>
       </c>
       <c r="J21" s="17">
-        <v>449</v>
+        <v>478</v>
       </c>
       <c r="K21" s="18">
-        <v>-0.668151447661</v>
+        <v>0.209205020920</v>
       </c>
       <c r="L21" s="18">
-        <v>-4.086021505376</v>
+        <v>-6.078431372549</v>
       </c>
       <c r="M21" s="18">
-        <v>16.145833333333</v>
+        <v>17.690417690417</v>
       </c>
       <c r="N21" s="18">
-        <v>-81.49377593361</v>
+        <v>-81.505791505791</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>2</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1189,7 +1189,7 @@
         <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>20</v>
@@ -1207,7 +1207,7 @@
         <v>240</v>
       </c>
       <c r="L22" s="15">
-        <v>13.333333333333</v>
+        <v>0</v>
       </c>
       <c r="M22" s="15">
         <v>112.5</v>
@@ -1223,35 +1223,35 @@
       <c r="C23" s="14">
         <v>1</v>
       </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
+      <c r="D23" s="14">
+        <v>3</v>
+      </c>
+      <c r="E23" s="15">
+        <v>-66.666666666666</v>
       </c>
       <c r="F23" s="14">
-        <v>5</v>
-      </c>
-      <c r="G23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H23" s="13" t="s">
-        <v>21</v>
+        <v>6</v>
+      </c>
+      <c r="G23" s="14">
+        <v>3</v>
+      </c>
+      <c r="H23" s="15">
+        <v>100</v>
       </c>
       <c r="I23" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J23" s="14">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K23" s="15">
-        <v>-26.315789473684</v>
+        <v>-31.818181818181</v>
       </c>
       <c r="L23" s="15">
-        <v>16.666666666666</v>
+        <v>7.142857142857</v>
       </c>
       <c r="M23" s="15">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D24" s="14">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="E24" s="15">
-        <v>-48.484848484848</v>
+        <v>25</v>
       </c>
       <c r="F24" s="14">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G24" s="14">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H24" s="15">
-        <v>-28.888888888888</v>
+        <v>-27.472527472527</v>
       </c>
       <c r="I24" s="14">
-        <v>283</v>
+        <v>303</v>
       </c>
       <c r="J24" s="14">
-        <v>312</v>
+        <v>328</v>
       </c>
       <c r="K24" s="15">
-        <v>-9.294871794871</v>
+        <v>-7.621951219512</v>
       </c>
       <c r="L24" s="15">
-        <v>-20.281690140845</v>
+        <v>-18.983957219251</v>
       </c>
       <c r="M24" s="15">
-        <v>17.427385892116</v>
+        <v>15.648854961832</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D25" s="14">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E25" s="15">
-        <v>-61.538461538461</v>
+        <v>14.285714285714</v>
       </c>
       <c r="F25" s="14">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G25" s="14">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H25" s="15">
-        <v>-62.857142857142</v>
+        <v>-48.484848484848</v>
       </c>
       <c r="I25" s="14">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="J25" s="14">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="K25" s="15">
-        <v>-51.754385964912</v>
+        <v>-47.933884297520</v>
       </c>
       <c r="L25" s="15">
-        <v>-66.257668711656</v>
+        <v>-62.721893491124</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="D26" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E26" s="15">
-        <v>62.5</v>
+        <v>400</v>
       </c>
       <c r="F26" s="14">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="G26" s="14">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H26" s="15">
-        <v>36.363636363636</v>
+        <v>96.774193548387</v>
       </c>
       <c r="I26" s="14">
-        <v>147</v>
+        <v>171</v>
       </c>
       <c r="J26" s="14">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="K26" s="15">
-        <v>-9.259259259259</v>
+        <v>2.395209580838</v>
       </c>
       <c r="L26" s="15">
-        <v>8.088235294117</v>
+        <v>18.75</v>
       </c>
       <c r="M26" s="15">
-        <v>26.724137931034</v>
+        <v>34.645669291338</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,22 +1385,22 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>3</v>
-      </c>
-      <c r="D27" s="14">
         <v>1</v>
       </c>
-      <c r="E27" s="15">
-        <v>200</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G27" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H27" s="15">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="I27" s="14">
         <v>19</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="14">
+        <v>1</v>
       </c>
       <c r="D28" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="F28" s="14">
         <v>6</v>
       </c>
       <c r="G28" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H28" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I28" s="14">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J28" s="14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K28" s="15">
-        <v>58.823529411764</v>
+        <v>52.631578947368</v>
       </c>
       <c r="L28" s="15">
-        <v>125</v>
+        <v>107.142857142857</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1548,8 +1548,8 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="14">
-        <v>1</v>
+      <c r="C31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>
@@ -1558,7 +1558,7 @@
         <v>21</v>
       </c>
       <c r="F31" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
@@ -1607,8 +1607,8 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="14">
-        <v>1</v>
+      <c r="C33" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-107pct.xlsx
+++ b/data/source/weekly/cs-en-us-107pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">17</t>
+      <t xml:space="preserve">18</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/20/2026</t>
+      <t xml:space="preserve">4/27/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/26/2026</t>
+      <t xml:space="preserve">5/3/2026</t>
     </r>
   </si>
   <si>
@@ -902,72 +902,72 @@
         <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G15" s="14">
         <v>1</v>
       </c>
       <c r="H15" s="15">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="I15" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J15" s="14">
         <v>4</v>
       </c>
       <c r="K15" s="15">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="L15" s="15">
-        <v>77.777777777777</v>
+        <v>88.888888888888</v>
       </c>
       <c r="M15" s="15">
-        <v>700</v>
+        <v>750</v>
       </c>
       <c r="N15" s="15">
-        <v>33.333333333333</v>
+        <v>41.666666666666</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
+      <c r="C16" s="14">
+        <v>11</v>
       </c>
       <c r="D16" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16" s="15">
-        <v>-100</v>
+        <v>1000</v>
       </c>
       <c r="F16" s="14">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="G16" s="14">
         <v>5</v>
       </c>
       <c r="H16" s="15">
-        <v>40</v>
+        <v>240</v>
       </c>
       <c r="I16" s="14">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="J16" s="14">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K16" s="15">
-        <v>0</v>
+        <v>27.777777777777</v>
       </c>
       <c r="L16" s="15">
-        <v>-16.666666666666</v>
+        <v>6.976744186046</v>
       </c>
       <c r="M16" s="15">
-        <v>-60.227272727272</v>
+        <v>-47.727272727272</v>
       </c>
       <c r="N16" s="15">
-        <v>-88.135593220339</v>
+        <v>-84.967320261437</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D17" s="14">
         <v>5</v>
       </c>
       <c r="E17" s="15">
-        <v>-20</v>
+        <v>40</v>
       </c>
       <c r="F17" s="14">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G17" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H17" s="15">
-        <v>80</v>
+        <v>64.705882352941</v>
       </c>
       <c r="I17" s="14">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="J17" s="14">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="K17" s="15">
-        <v>-7.692307692307</v>
+        <v>-4.819277108433</v>
       </c>
       <c r="L17" s="15">
-        <v>-21.739130434782</v>
+        <v>-17.708333333333</v>
       </c>
       <c r="M17" s="15">
-        <v>157.142857142857</v>
+        <v>163.333333333333</v>
       </c>
       <c r="N17" s="15">
-        <v>4.347826086956</v>
+        <v>6.756756756756</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,37 +1019,37 @@
         <v>5</v>
       </c>
       <c r="D18" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E18" s="15">
-        <v>25</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F18" s="14">
+        <v>19</v>
+      </c>
+      <c r="G18" s="14">
         <v>16</v>
       </c>
-      <c r="G18" s="14">
-        <v>20</v>
-      </c>
       <c r="H18" s="15">
-        <v>-20</v>
+        <v>18.75</v>
       </c>
       <c r="I18" s="14">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="J18" s="14">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="K18" s="15">
-        <v>-37.349397590361</v>
+        <v>-35.955056179775</v>
       </c>
       <c r="L18" s="15">
-        <v>-32.467532467532</v>
+        <v>-28.75</v>
       </c>
       <c r="M18" s="15">
-        <v>-31.578947368421</v>
+        <v>-30.487804878048</v>
       </c>
       <c r="N18" s="15">
-        <v>-89.278350515463</v>
+        <v>-88.801571709233</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D19" s="14">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E19" s="15">
-        <v>110</v>
+        <v>-36.842105263157</v>
       </c>
       <c r="F19" s="14">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G19" s="14">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="H19" s="15">
-        <v>48.979591836734</v>
+        <v>41.509433962264</v>
       </c>
       <c r="I19" s="14">
-        <v>208</v>
+        <v>224</v>
       </c>
       <c r="J19" s="14">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="K19" s="15">
-        <v>30</v>
+        <v>25.139664804469</v>
       </c>
       <c r="L19" s="15">
-        <v>8.900523560209</v>
+        <v>11.442786069651</v>
       </c>
       <c r="M19" s="15">
-        <v>38.666666666666</v>
+        <v>41.772151898734</v>
       </c>
       <c r="N19" s="15">
-        <v>12.432432432432</v>
+        <v>12.562814070351</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,37 +1101,37 @@
         <v>4</v>
       </c>
       <c r="D20" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E20" s="15">
-        <v>-50</v>
+        <v>-20</v>
       </c>
       <c r="F20" s="14">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="G20" s="14">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H20" s="15">
-        <v>-30</v>
+        <v>-55.172413793103</v>
       </c>
       <c r="I20" s="14">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="J20" s="14">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="K20" s="15">
-        <v>-17.391304347826</v>
+        <v>-17.5</v>
       </c>
       <c r="L20" s="15">
-        <v>-2.061855670103</v>
+        <v>-1.980198019801</v>
       </c>
       <c r="M20" s="15">
-        <v>53.225806451612</v>
+        <v>57.142857142857</v>
       </c>
       <c r="N20" s="15">
-        <v>-93.839169909208</v>
+        <v>-93.992718446601</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D21" s="17">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="E21" s="18">
-        <v>20.689655172413</v>
+        <v>11.111111111111</v>
       </c>
       <c r="F21" s="17">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="G21" s="17">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H21" s="18">
-        <v>25</v>
+        <v>31.404958677686</v>
       </c>
       <c r="I21" s="17">
-        <v>479</v>
+        <v>523</v>
       </c>
       <c r="J21" s="17">
-        <v>478</v>
+        <v>514</v>
       </c>
       <c r="K21" s="18">
-        <v>0.209205020920</v>
+        <v>1.750972762645</v>
       </c>
       <c r="L21" s="18">
-        <v>-6.078431372549</v>
+        <v>-1.691729323308</v>
       </c>
       <c r="M21" s="18">
-        <v>17.690417690417</v>
+        <v>23.349056603773</v>
       </c>
       <c r="N21" s="18">
-        <v>-81.505791505791</v>
+        <v>-80.981818181818</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="C22" s="14">
+        <v>1</v>
+      </c>
+      <c r="D22" s="14">
+        <v>2</v>
+      </c>
+      <c r="E22" s="15">
+        <v>-50</v>
       </c>
       <c r="F22" s="14">
         <v>4</v>
       </c>
-      <c r="G22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H22" s="13" t="s">
-        <v>21</v>
+      <c r="G22" s="14">
+        <v>2</v>
+      </c>
+      <c r="H22" s="15">
+        <v>100</v>
       </c>
       <c r="I22" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J22" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K22" s="15">
-        <v>240</v>
+        <v>157.142857142857</v>
       </c>
       <c r="L22" s="15">
-        <v>0</v>
+        <v>5.882352941176</v>
       </c>
       <c r="M22" s="15">
-        <v>112.5</v>
+        <v>125</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,14 +1220,14 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="14">
-        <v>1</v>
-      </c>
-      <c r="D23" s="14">
-        <v>3</v>
-      </c>
-      <c r="E23" s="15">
-        <v>-66.666666666666</v>
+      <c r="C23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F23" s="14">
         <v>6</v>
@@ -1251,7 +1251,7 @@
         <v>7.142857142857</v>
       </c>
       <c r="M23" s="15">
-        <v>50</v>
+        <v>36.363636363636</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D24" s="14">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E24" s="15">
-        <v>25</v>
+        <v>-20.833333333333</v>
       </c>
       <c r="F24" s="14">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G24" s="14">
         <v>91</v>
       </c>
       <c r="H24" s="15">
-        <v>-27.472527472527</v>
+        <v>-26.373626373626</v>
       </c>
       <c r="I24" s="14">
-        <v>303</v>
+        <v>318</v>
       </c>
       <c r="J24" s="14">
-        <v>328</v>
+        <v>352</v>
       </c>
       <c r="K24" s="15">
-        <v>-7.621951219512</v>
+        <v>-9.659090909090</v>
       </c>
       <c r="L24" s="15">
-        <v>-18.983957219251</v>
+        <v>-20.895522388059</v>
       </c>
       <c r="M24" s="15">
-        <v>15.648854961832</v>
+        <v>12.367491166077</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D25" s="14">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E25" s="15">
-        <v>14.285714285714</v>
+        <v>-81.818181818181</v>
       </c>
       <c r="F25" s="14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G25" s="14">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="H25" s="15">
-        <v>-48.484848484848</v>
+        <v>-47.222222222222</v>
       </c>
       <c r="I25" s="14">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="J25" s="14">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="K25" s="15">
-        <v>-47.933884297520</v>
+        <v>-50.757575757575</v>
       </c>
       <c r="L25" s="15">
-        <v>-62.721893491124</v>
+        <v>-64.480874316939</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="D26" s="14">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E26" s="15">
-        <v>400</v>
+        <v>-25</v>
       </c>
       <c r="F26" s="14">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G26" s="14">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H26" s="15">
-        <v>96.774193548387</v>
+        <v>77.142857142857</v>
       </c>
       <c r="I26" s="14">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="J26" s="14">
-        <v>167</v>
+        <v>183</v>
       </c>
       <c r="K26" s="15">
-        <v>2.395209580838</v>
+        <v>0</v>
       </c>
       <c r="L26" s="15">
-        <v>18.75</v>
+        <v>21.192052980132</v>
       </c>
       <c r="M26" s="15">
-        <v>34.645669291338</v>
+        <v>29.787234042553</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1394,25 +1394,25 @@
         <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G27" s="14">
         <v>1</v>
       </c>
       <c r="H27" s="15">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="I27" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J27" s="14">
         <v>5</v>
       </c>
       <c r="K27" s="15">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="L27" s="15">
-        <v>46.153846153846</v>
+        <v>53.846153846153</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D28" s="14">
         <v>2</v>
       </c>
       <c r="E28" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="F28" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G28" s="14">
         <v>6</v>
       </c>
       <c r="H28" s="15">
-        <v>0</v>
+        <v>16.666666666666</v>
       </c>
       <c r="I28" s="14">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J28" s="14">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K28" s="15">
-        <v>52.631578947368</v>
+        <v>47.619047619047</v>
       </c>
       <c r="L28" s="15">
-        <v>107.142857142857</v>
+        <v>106.666666666667</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1558,7 +1558,7 @@
         <v>21</v>
       </c>
       <c r="F31" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
@@ -1567,16 +1567,16 @@
         <v>21</v>
       </c>
       <c r="I31" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J31" s="14">
         <v>3</v>
       </c>
       <c r="K31" s="15">
-        <v>133.333333333333</v>
+        <v>166.666666666667</v>
       </c>
       <c r="L31" s="15">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-107pct.xlsx
+++ b/data/source/weekly/cs-en-us-107pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">18</t>
+      <t xml:space="preserve">19</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/27/2026</t>
+      <t xml:space="preserve">5/4/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">5/3/2026</t>
+      <t xml:space="preserve">5/10/2026</t>
     </r>
   </si>
   <si>
@@ -879,7 +879,7 @@
         <v>-66.666666666666</v>
       </c>
       <c r="L14" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M14" s="15">
         <v>0</v>
@@ -892,32 +892,32 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>1</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="14">
+        <v>2</v>
+      </c>
+      <c r="E15" s="15">
+        <v>-100</v>
       </c>
       <c r="F15" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G15" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H15" s="15">
-        <v>600</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I15" s="14">
         <v>17</v>
       </c>
       <c r="J15" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K15" s="15">
-        <v>325</v>
+        <v>183.333333333333</v>
       </c>
       <c r="L15" s="15">
         <v>88.888888888888</v>
@@ -926,7 +926,7 @@
         <v>750</v>
       </c>
       <c r="N15" s="15">
-        <v>41.666666666666</v>
+        <v>30.769230769230</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,13 +934,13 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D16" s="14">
         <v>1</v>
       </c>
       <c r="E16" s="15">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="F16" s="14">
         <v>17</v>
@@ -952,22 +952,22 @@
         <v>240</v>
       </c>
       <c r="I16" s="14">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J16" s="14">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K16" s="15">
-        <v>27.777777777777</v>
+        <v>29.729729729729</v>
       </c>
       <c r="L16" s="15">
-        <v>6.976744186046</v>
+        <v>9.090909090909</v>
       </c>
       <c r="M16" s="15">
-        <v>-47.727272727272</v>
+        <v>-49.473684210526</v>
       </c>
       <c r="N16" s="15">
-        <v>-84.967320261437</v>
+        <v>-84.905660377358</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D17" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E17" s="15">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F17" s="14">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="G17" s="14">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H17" s="15">
-        <v>64.705882352941</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I17" s="14">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="J17" s="14">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="K17" s="15">
-        <v>-4.819277108433</v>
+        <v>-5.747126436781</v>
       </c>
       <c r="L17" s="15">
-        <v>-17.708333333333</v>
+        <v>-20.388349514563</v>
       </c>
       <c r="M17" s="15">
-        <v>163.333333333333</v>
+        <v>156.25</v>
       </c>
       <c r="N17" s="15">
-        <v>6.756756756756</v>
+        <v>3.797468354430</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D18" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E18" s="15">
-        <v>-16.666666666666</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F18" s="14">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G18" s="14">
         <v>16</v>
       </c>
       <c r="H18" s="15">
-        <v>18.75</v>
+        <v>-6.25</v>
       </c>
       <c r="I18" s="14">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J18" s="14">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K18" s="15">
-        <v>-35.955056179775</v>
+        <v>-36.956521739130</v>
       </c>
       <c r="L18" s="15">
-        <v>-28.75</v>
+        <v>-30.120481927710</v>
       </c>
       <c r="M18" s="15">
-        <v>-30.487804878048</v>
+        <v>-34.090909090909</v>
       </c>
       <c r="N18" s="15">
-        <v>-88.801571709233</v>
+        <v>-89.097744360902</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
+        <v>7</v>
+      </c>
+      <c r="D19" s="14">
         <v>12</v>
       </c>
-      <c r="D19" s="14">
-        <v>19</v>
-      </c>
       <c r="E19" s="15">
-        <v>-36.842105263157</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="F19" s="14">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="G19" s="14">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="H19" s="15">
-        <v>41.509433962264</v>
+        <v>12.727272727272</v>
       </c>
       <c r="I19" s="14">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="J19" s="14">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="K19" s="15">
-        <v>25.139664804469</v>
+        <v>20.942408376963</v>
       </c>
       <c r="L19" s="15">
-        <v>11.442786069651</v>
+        <v>10</v>
       </c>
       <c r="M19" s="15">
-        <v>41.772151898734</v>
+        <v>33.526011560693</v>
       </c>
       <c r="N19" s="15">
-        <v>12.562814070351</v>
+        <v>11.057692307692</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D20" s="14">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E20" s="15">
-        <v>-20</v>
+        <v>22.222222222222</v>
       </c>
       <c r="F20" s="14">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="G20" s="14">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H20" s="15">
-        <v>-55.172413793103</v>
+        <v>-26.666666666666</v>
       </c>
       <c r="I20" s="14">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="J20" s="14">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="K20" s="15">
-        <v>-17.5</v>
+        <v>-14.728682170542</v>
       </c>
       <c r="L20" s="15">
-        <v>-1.980198019801</v>
+        <v>-0.900900900900</v>
       </c>
       <c r="M20" s="15">
-        <v>57.142857142857</v>
+        <v>52.777777777777</v>
       </c>
       <c r="N20" s="15">
-        <v>-93.992718446601</v>
+        <v>-93.699885452462</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="D21" s="17">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="E21" s="18">
-        <v>11.111111111111</v>
+        <v>-19.354838709677</v>
       </c>
       <c r="F21" s="17">
-        <v>159</v>
+        <v>140</v>
       </c>
       <c r="G21" s="17">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="H21" s="18">
-        <v>31.404958677686</v>
+        <v>12.903225806451</v>
       </c>
       <c r="I21" s="17">
-        <v>523</v>
+        <v>547</v>
       </c>
       <c r="J21" s="17">
-        <v>514</v>
+        <v>545</v>
       </c>
       <c r="K21" s="18">
-        <v>1.750972762645</v>
+        <v>0.366972477064</v>
       </c>
       <c r="L21" s="18">
-        <v>-1.691729323308</v>
+        <v>-2.841918294849</v>
       </c>
       <c r="M21" s="18">
-        <v>23.349056603773</v>
+        <v>18.142548596112</v>
       </c>
       <c r="N21" s="18">
-        <v>-80.981818181818</v>
+        <v>-81.124913733609</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
+      <c r="C22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="14">
         <v>1</v>
       </c>
-      <c r="D22" s="14">
+      <c r="E22" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F22" s="14">
         <v>2</v>
       </c>
-      <c r="E22" s="15">
-        <v>-50</v>
-      </c>
-      <c r="F22" s="14">
-        <v>4</v>
-      </c>
       <c r="G22" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H22" s="15">
-        <v>100</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I22" s="14">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J22" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K22" s="15">
-        <v>157.142857142857</v>
+        <v>112.5</v>
       </c>
       <c r="L22" s="15">
-        <v>5.882352941176</v>
+        <v>0</v>
       </c>
       <c r="M22" s="15">
-        <v>125</v>
+        <v>112.5</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1230,13 +1230,13 @@
         <v>21</v>
       </c>
       <c r="F23" s="14">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G23" s="14">
         <v>3</v>
       </c>
       <c r="H23" s="15">
-        <v>100</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I23" s="14">
         <v>15</v>
@@ -1248,7 +1248,7 @@
         <v>-31.818181818181</v>
       </c>
       <c r="L23" s="15">
-        <v>7.142857142857</v>
+        <v>-6.25</v>
       </c>
       <c r="M23" s="15">
         <v>36.363636363636</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D24" s="14">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E24" s="15">
-        <v>-20.833333333333</v>
+        <v>-17.647058823529</v>
       </c>
       <c r="F24" s="14">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="G24" s="14">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H24" s="15">
-        <v>-26.373626373626</v>
+        <v>-21.111111111111</v>
       </c>
       <c r="I24" s="14">
-        <v>318</v>
+        <v>332</v>
       </c>
       <c r="J24" s="14">
-        <v>352</v>
+        <v>369</v>
       </c>
       <c r="K24" s="15">
-        <v>-9.659090909090</v>
+        <v>-10.027100271002</v>
       </c>
       <c r="L24" s="15">
-        <v>-20.895522388059</v>
+        <v>-20.952380952381</v>
       </c>
       <c r="M24" s="15">
-        <v>12.367491166077</v>
+        <v>8.852459016393</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D25" s="14">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E25" s="15">
-        <v>-81.818181818181</v>
+        <v>0</v>
       </c>
       <c r="F25" s="14">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G25" s="14">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H25" s="15">
-        <v>-47.222222222222</v>
+        <v>-50</v>
       </c>
       <c r="I25" s="14">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="J25" s="14">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="K25" s="15">
-        <v>-50.757575757575</v>
+        <v>-50.370370370370</v>
       </c>
       <c r="L25" s="15">
-        <v>-64.480874316939</v>
+        <v>-65.104166666666</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D26" s="14">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E26" s="15">
-        <v>-25</v>
+        <v>25</v>
       </c>
       <c r="F26" s="14">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G26" s="14">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H26" s="15">
-        <v>77.142857142857</v>
+        <v>59.459459459459</v>
       </c>
       <c r="I26" s="14">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="J26" s="14">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="K26" s="15">
-        <v>0</v>
+        <v>0.523560209424</v>
       </c>
       <c r="L26" s="15">
-        <v>21.192052980132</v>
+        <v>20</v>
       </c>
       <c r="M26" s="15">
-        <v>29.787234042553</v>
+        <v>27.152317880794</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,32 +1384,32 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>1</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="14">
+        <v>2</v>
+      </c>
+      <c r="E27" s="15">
+        <v>-100</v>
       </c>
       <c r="F27" s="14">
+        <v>4</v>
+      </c>
+      <c r="G27" s="14">
+        <v>3</v>
+      </c>
+      <c r="H27" s="15">
+        <v>33.333333333333</v>
+      </c>
+      <c r="I27" s="14">
+        <v>20</v>
+      </c>
+      <c r="J27" s="14">
         <v>7</v>
       </c>
-      <c r="G27" s="14">
-        <v>1</v>
-      </c>
-      <c r="H27" s="15">
-        <v>600</v>
-      </c>
-      <c r="I27" s="14">
-        <v>20</v>
-      </c>
-      <c r="J27" s="14">
-        <v>5</v>
-      </c>
       <c r="K27" s="15">
-        <v>300</v>
+        <v>185.714285714286</v>
       </c>
       <c r="L27" s="15">
         <v>53.846153846153</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D28" s="14">
         <v>2</v>
       </c>
       <c r="E28" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="F28" s="14">
+        <v>5</v>
+      </c>
+      <c r="G28" s="14">
         <v>7</v>
       </c>
-      <c r="G28" s="14">
-        <v>6</v>
-      </c>
       <c r="H28" s="15">
-        <v>16.666666666666</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="I28" s="14">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J28" s="14">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K28" s="15">
-        <v>47.619047619047</v>
+        <v>39.130434782608</v>
       </c>
       <c r="L28" s="15">
-        <v>106.666666666667</v>
+        <v>100</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1551,29 +1551,29 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="D31" s="14">
+        <v>1</v>
+      </c>
+      <c r="E31" s="15">
+        <v>-100</v>
       </c>
       <c r="F31" s="14">
-        <v>3</v>
-      </c>
-      <c r="G31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H31" s="13" t="s">
-        <v>21</v>
+        <v>2</v>
+      </c>
+      <c r="G31" s="14">
+        <v>1</v>
+      </c>
+      <c r="H31" s="15">
+        <v>100</v>
       </c>
       <c r="I31" s="14">
         <v>8</v>
       </c>
       <c r="J31" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K31" s="15">
-        <v>166.666666666667</v>
+        <v>100</v>
       </c>
       <c r="L31" s="15">
         <v>700</v>
